--- a/doc/BotruyvanGEO-Paris/02-implant.xlsx
+++ b/doc/BotruyvanGEO-Paris/02-implant.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,18 +89,6 @@
       <color rgb="00131A2E"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="009AA3BD"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="009AA3BD"/>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -161,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -247,14 +235,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -267,9 +252,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -940,16 +922,16 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>49</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.451</v>
+        <v>0.4275</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1842</v>
+        <v>1818</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -973,7 +955,7 @@
         <v>0.2</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>459</v>
+        <v>534</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1008,48 +990,48 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Mất 1 răng cửa</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.0667</v>
+        <v>0.0824</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Ưu tiên thẩm mỹ và thời gian — sợ hở lợi, sợ màu mão khác răng thật, sợ mất răng cửa suốt mấy tháng chờ tích hợp.</t>
+          <t>Tiểu đường, loãng xương, tim mạch, đang dùng thuốc chống loãng xương. Câu hỏi luôn là “người như tôi có làm được không”.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Mất nhiều răng / toàn hàm</t>
+          <t>Mất 1 răng cửa</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.0706</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Chi phí lớn nhất, thường là người trên 50 tuổi. Phân vân All-On với cấy từng trụ rời; cần dẫn sang bộ All-On 4/6.</t>
+          <t>Ưu tiên thẩm mỹ và thời gian — sợ hở lợi, sợ màu mão khác răng thật, sợ mất răng cửa suốt mấy tháng chờ tích hợp.</t>
         </is>
       </c>
     </row>
@@ -1060,16 +1042,16 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.0706</v>
+        <v>0.0549</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1080,24 +1062,24 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Bệnh lý nền &amp; người cao tuổi</t>
+          <t>Mất nhiều răng / toàn hàm</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.0667</v>
+        <v>0.0784</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Tiểu đường, loãng xương, tim mạch, đang dùng thuốc chống loãng xương. Câu hỏi luôn là “người như tôi có làm được không”.</t>
+          <t>Chi phí lớn nhất, thường là người trên 50 tuổi. Phân vân All-On với cấy từng trụ rời; cần dẫn sang bộ All-On 4/6.</t>
         </is>
       </c>
     </row>
@@ -1108,16 +1090,16 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.0078</v>
+        <v>0.0275</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -2008,6 +1990,11 @@
           <t>ĐIỂM ƯU TIÊN = Giá trị DT (Cao 3 · TB 2 · Thấp 1) × Nhiệt độ (Hot 3 · Warm 2 · Existing 2 · Cold 1) × Ưu tiên (P1 3 · P2 2 · P3 1) × CƠ HỘI GEO. ⚠ Paris chưa có mốc traffic AI → CƠ HỘI GEO = 1 cho mọi cụm; chấm lại sau tháng Setup.</t>
         </is>
       </c>
+      <c r="S3" s="20" t="inlineStr">
+        <is>
+          <t>Hai cột điểm có nguồn khác nhau và LỆCH NHAU LÀ BÌNH THƯỜNG: «ĐIỂM CỤM» cộng bottom-up từ 17 truy vấn của cụm; «% ĐIỂM (chỉ mục)» lấy từ knowledge/geo-bo-truy-van-index.md — đây là con số Agent dùng để lập kế hoạch. Sau tháng Setup có mốc traffic thật thì chấm lại CƠ HỘI GEO và hợp nhất hai nguồn.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -2881,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="9" t="n">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="AA10" s="9" t="n">
         <v>0.09</v>
@@ -3005,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="13" t="n">
-        <v>204</v>
+        <v>357</v>
       </c>
       <c r="AA11" s="13" t="n">
         <v>0.08</v>
@@ -3129,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="AA12" s="9" t="n">
         <v>0.07000000000000001</v>
@@ -3253,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AA13" s="13" t="n">
         <v>0.04</v>
@@ -3377,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>102</v>
+        <v>348</v>
       </c>
       <c r="AA14" s="9" t="n">
         <v>0.03</v>
@@ -3625,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="9" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="AA16" s="9" t="n">
         <v>0.05</v>
@@ -3749,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="AA17" s="13" t="n">
         <v>0.03</v>
@@ -9797,10 +9784,14 @@
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E90" s="28" t="inlineStr"/>
+          <t>nên trồng răng implant ở đâu uy tín</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F90" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -9808,7 +9799,7 @@
       </c>
       <c r="G90" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
@@ -9828,12 +9819,16 @@
       </c>
       <c r="K90" s="28" t="inlineStr"/>
       <c r="L90" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M90" s="10" t="inlineStr"/>
-      <c r="N90" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M90" s="10" t="inlineStr">
+        <is>
+          <t>trồng implant ở đâu uy tín</t>
+        </is>
+      </c>
+      <c r="N90" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: đưa bộ 6 tiêu chí kiểm chứng được thay vì tự khen — giấy phép của chính cơ sở, chứng chỉ hành nghề của bác sĩ trực tiếp làm, có CT Conebeam tại chỗ, vật liệu tra được mã, báo giá tách 3 cấu phần bằng văn bản, chính sách bảo hành ghi rõ điều kiện loại trừ.</t>
         </is>
       </c>
       <c r="O90" s="10" t="inlineStr">
@@ -9843,7 +9838,7 @@
       </c>
       <c r="P90" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R6 · Không nêu tên hạ thấp; R3 đúng giấy phép cơ sở</t>
         </is>
       </c>
       <c r="Q90" s="10" t="inlineStr">
@@ -9870,10 +9865,14 @@
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E91" s="28" t="inlineStr"/>
+          <t>Em nên chọn bệnh viện Răng Hàm Mặt hay nha khoa tư để trồng implant ạ?</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F91" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -9881,7 +9880,7 @@
       </c>
       <c r="G91" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
@@ -9901,12 +9900,16 @@
       </c>
       <c r="K91" s="28" t="inlineStr"/>
       <c r="L91" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M91" s="10" t="inlineStr"/>
-      <c r="N91" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>bệnh viện hay nha khoa tư</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: so sánh theo khung tiêu chí khách quan — phạm vi chuyên môn được cấp phép, thời gian chờ, mức độ theo sát của một bác sĩ xuyên suốt, và khả năng xử lý biến chứng. Nêu cả ưu điểm của tuyến công. KHÔNG kết luận bên nào hơn.</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
@@ -9916,7 +9919,7 @@
       </c>
       <c r="P91" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R6 · Khung tiêu chí, không phán xét</t>
         </is>
       </c>
       <c r="Q91" s="10" t="inlineStr">
@@ -9943,10 +9946,14 @@
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E92" s="28" t="inlineStr"/>
+          <t>làm sao biết bác sĩ có chứng chỉ hành nghề implant</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -9954,7 +9961,7 @@
       </c>
       <c r="G92" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
@@ -9974,12 +9981,16 @@
       </c>
       <c r="K92" s="28" t="inlineStr"/>
       <c r="L92" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M92" s="10" t="inlineStr"/>
-      <c r="N92" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M92" s="10" t="inlineStr">
+        <is>
+          <t>chứng chỉ hành nghề bác sĩ</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: hướng dẫn 3 bước — yêu cầu xem chứng chỉ hành nghề bản gốc, đối chiếu phạm vi hoạt động chuyên môn ghi trên đó, và yêu cầu ghi tên bác sĩ trực tiếp thực hiện vào hồ sơ trước khi làm.</t>
         </is>
       </c>
       <c r="O92" s="10" t="inlineStr">
@@ -9989,7 +10000,7 @@
       </c>
       <c r="P92" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R4 · Chỉ nêu bác sĩ có hồ sơ</t>
         </is>
       </c>
       <c r="Q92" s="10" t="inlineStr">
@@ -10016,18 +10027,22 @@
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E93" s="28" t="inlineStr"/>
+          <t>nha khoa có CT Conebeam tại chỗ có quan trọng không</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F93" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G93" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H93" s="28" t="inlineStr">
@@ -10049,10 +10064,14 @@
       <c r="L93" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="M93" s="10" t="inlineStr"/>
-      <c r="N93" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M93" s="10" t="inlineStr">
+        <is>
+          <t>CT Conebeam tại chỗ</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: quan trọng vì hai lý do thực tế — đo được khoảng cách tới ống thần kinh và chiều cao xương dưới xoang ngay trước mổ, và kiểm tra lại được vị trí trụ ngay sau cấy. Gửi đi chụp ngoài vẫn làm được nhưng mất thêm buổi.</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
@@ -10089,10 +10108,14 @@
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E94" s="28" t="inlineStr"/>
+          <t>Phòng khám nói bác sĩ A tư vấn nhưng hôm làm lại là bác sĩ khác. Như vậy có bình thường không ạ?</t>
+        </is>
+      </c>
+      <c r="E94" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -10100,7 +10123,7 @@
       </c>
       <c r="G94" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
@@ -10120,12 +10143,16 @@
       </c>
       <c r="K94" s="28" t="inlineStr"/>
       <c r="L94" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M94" s="10" t="inlineStr"/>
-      <c r="N94" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M94" s="10" t="inlineStr">
+        <is>
+          <t>bác sĩ tư vấn khác bác sĩ làm</t>
+        </is>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khách có quyền biết và có quyền yêu cầu ghi rõ tên bác sĩ trực tiếp thực hiện vào hồ sơ trước khi làm. Hướng dẫn cách hỏi rõ ngay từ buổi tư vấn. Không bình luận về nơi cụ thể.</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
@@ -10135,7 +10162,7 @@
       </c>
       <c r="P94" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R4 · R6 · Không phán xét cơ sở khác</t>
         </is>
       </c>
       <c r="Q94" s="10" t="inlineStr">
@@ -10162,13 +10189,17 @@
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E95" s="28" t="inlineStr"/>
+          <t>nên chọn nha khoa gần nhà hay nha khoa lớn ở xa</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F95" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G95" s="28" t="inlineStr">
@@ -10193,12 +10224,16 @@
       </c>
       <c r="K95" s="28" t="inlineStr"/>
       <c r="L95" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M95" s="10" t="inlineStr"/>
-      <c r="N95" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M95" s="10" t="inlineStr">
+        <is>
+          <t>chọn nha khoa gần hay xa</t>
+        </is>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: implant cần 3–6 tháng theo dõi với nhiều lần tái khám, nên khoảng cách là yếu tố thật sự ảnh hưởng kết quả. Gợi ý khung quyết định: cấy ở nơi đủ năng lực kỹ thuật, tái khám ở cơ sở gần nếu cùng hệ thống.</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
@@ -10213,7 +10248,7 @@
       </c>
       <c r="Q95" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Khách tỉnh &amp; Việt kiều</t>
         </is>
       </c>
     </row>
@@ -10235,10 +10270,14 @@
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="inlineStr"/>
+          <t>nha khoa nào trồng implant tốt ở Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -10246,7 +10285,7 @@
       </c>
       <c r="G96" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
@@ -10266,12 +10305,16 @@
       </c>
       <c r="K96" s="28" t="inlineStr"/>
       <c r="L96" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M96" s="10" t="inlineStr"/>
-      <c r="N96" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M96" s="10" t="inlineStr">
+        <is>
+          <t>trồng implant Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: trang local phải nêu NAP của chính cơ sở tại Đà Nẵng, số giấy phép do Sở Y tế Đà Nẵng cấp, và phạm vi chuyên môn của cơ sở đó. Kỹ thuật ngoài phạm vi thì ghi rõ điều hướng về cơ sở thực hiện.</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
@@ -10281,7 +10324,7 @@
       </c>
       <c r="P96" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R3 · Giấy phép của chính cơ sở đó</t>
         </is>
       </c>
       <c r="Q96" s="10" t="inlineStr">
@@ -10308,10 +10351,14 @@
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="inlineStr"/>
+          <t>cách nhận biết nha khoa kém chất lượng</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F97" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -10319,7 +10366,7 @@
       </c>
       <c r="G97" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H97" s="28" t="inlineStr">
@@ -10339,12 +10386,16 @@
       </c>
       <c r="K97" s="28" t="inlineStr"/>
       <c r="L97" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M97" s="10" t="inlineStr"/>
-      <c r="N97" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M97" s="10" t="inlineStr">
+        <is>
+          <t>nhận biết nha khoa kém</t>
+        </is>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nêu dấu hiệu theo HÀNH VI chứ không theo tên — báo giá trọn gói mà không tách cấu phần, không chụp phim đã báo giá, không cho xem mã trụ, ép đặt cọc trong buổi đầu, không có phiếu bảo hành bằng văn bản.</t>
         </is>
       </c>
       <c r="O97" s="10" t="inlineStr">
@@ -10354,7 +10405,7 @@
       </c>
       <c r="P97" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R6 · Mô tả hành vi, không nêu tên</t>
         </is>
       </c>
       <c r="Q97" s="10" t="inlineStr">
@@ -10381,13 +10432,17 @@
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E98" s="28" t="inlineStr"/>
+          <t>có nên trồng implant ở phòng khám nhỏ không</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F98" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G98" s="28" t="inlineStr">
@@ -10412,12 +10467,16 @@
       </c>
       <c r="K98" s="28" t="inlineStr"/>
       <c r="L98" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M98" s="10" t="inlineStr"/>
-      <c r="N98" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M98" s="10" t="inlineStr">
+        <is>
+          <t>implant ở phòng khám nhỏ</t>
+        </is>
+      </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: quy mô không phải tiêu chí — điều quyết định là phạm vi chuyên môn được cấp phép, thiết bị chẩn đoán và năng lực xử lý biến chứng. Nêu rõ ca cần ghép xương lớn hoặc nâng xoang hở cần cơ sở có phạm vi tương ứng.</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
@@ -10454,18 +10513,22 @@
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E99" s="28" t="inlineStr"/>
+          <t>trồng implant có cần chọn bác sĩ chuyên sâu implant không</t>
+        </is>
+      </c>
+      <c r="E99" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F99" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G99" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H99" s="28" t="inlineStr">
@@ -10487,10 +10550,14 @@
       <c r="L99" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="M99" s="10" t="inlineStr"/>
-      <c r="N99" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M99" s="10" t="inlineStr">
+        <is>
+          <t>bác sĩ chuyên sâu implant</t>
+        </is>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có — implant là lĩnh vực mà số ca đã làm tương quan rõ với kết quả. Gợi ý câu hỏi cụ thể để khách hỏi: bác sĩ đã làm bao nhiêu ca dạng của tôi, có làm ca tháo/cấy lại không.</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
@@ -10527,13 +10594,17 @@
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E100" s="28" t="inlineStr"/>
+          <t>nha khoa nhận bảo hành implant của nơi khác không</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G100" s="28" t="inlineStr">
@@ -10558,12 +10629,16 @@
       </c>
       <c r="K100" s="28" t="inlineStr"/>
       <c r="L100" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M100" s="10" t="inlineStr"/>
-      <c r="N100" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M100" s="10" t="inlineStr">
+        <is>
+          <t>bảo hành implant nơi khác</t>
+        </is>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: bảo hành của phòng khám thường không chuyển được sang nơi khác; bảo hành của HÃNG thì gắn với trụ nên có thể dùng ở cơ sở cùng hệ. Hướng dẫn khách giữ thẻ implant và hoá đơn.</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
@@ -10573,7 +10648,7 @@
       </c>
       <c r="P100" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R6 · Không bình luận nơi cũ</t>
         </is>
       </c>
       <c r="Q100" s="10" t="inlineStr">
@@ -10600,13 +10675,17 @@
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E101" s="28" t="inlineStr"/>
+          <t>đi khám implant lần đầu cần chuẩn bị gì</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F101" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G101" s="28" t="inlineStr">
@@ -10631,12 +10710,16 @@
       </c>
       <c r="K101" s="28" t="inlineStr"/>
       <c r="L101" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M101" s="10" t="inlineStr"/>
-      <c r="N101" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M101" s="10" t="inlineStr">
+        <is>
+          <t>khám implant lần đầu</t>
+        </is>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: mang theo phim cũ nếu có, danh sách thuốc đang dùng, hồ sơ bệnh nền. Đặt sẵn 5 câu hỏi: ai làm, trụ hãng nào, báo giá tách mấy khoản, mất bao lâu, bảo hành điều kiện gì.</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
@@ -10673,10 +10756,14 @@
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E102" s="28" t="inlineStr"/>
+          <t>nha khoa Paris cơ sở nào làm được implant</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F102" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -10684,7 +10771,7 @@
       </c>
       <c r="G102" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
@@ -10704,12 +10791,16 @@
       </c>
       <c r="K102" s="28" t="inlineStr"/>
       <c r="L102" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M102" s="10" t="inlineStr"/>
-      <c r="N102" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M102" s="10" t="inlineStr">
+        <is>
+          <t>cơ sở Paris làm implant</t>
+        </is>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: liệt kê theo phạm vi chuyên môn thực tế của từng cơ sở, lấy tại trang tìm phòng khám khi chạy. Không nêu chung cho cả hệ thống nếu chỉ một số cơ sở thực hiện được.</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
@@ -10719,7 +10810,7 @@
       </c>
       <c r="P102" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R3 · Đúng phạm vi từng cơ sở</t>
         </is>
       </c>
       <c r="Q102" s="10" t="inlineStr">
@@ -10746,13 +10837,17 @@
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E103" s="28" t="inlineStr"/>
+          <t>có nên tin review trên mạng khi chọn nha khoa implant</t>
+        </is>
+      </c>
+      <c r="E103" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F103" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G103" s="28" t="inlineStr">
@@ -10777,12 +10872,16 @@
       </c>
       <c r="K103" s="28" t="inlineStr"/>
       <c r="L103" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M103" s="10" t="inlineStr"/>
-      <c r="N103" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M103" s="10" t="inlineStr">
+        <is>
+          <t>review nha khoa implant</t>
+        </is>
+      </c>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dạy cách đọc review — ưu tiên review mô tả quá trình và mốc thời gian, có nhắc tên bác sĩ và loại trụ; cảnh giác với review một câu và review dồn trong vài ngày.</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
@@ -10819,13 +10918,17 @@
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E104" s="28" t="inlineStr"/>
+          <t>trồng implant xong chuyển tỉnh khác thì tái khám ở đâu</t>
+        </is>
+      </c>
+      <c r="E104" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
@@ -10850,12 +10953,16 @@
       </c>
       <c r="K104" s="28" t="inlineStr"/>
       <c r="L104" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M104" s="10" t="inlineStr"/>
-      <c r="N104" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M104" s="10" t="inlineStr">
+        <is>
+          <t>tái khám implant khi chuyển tỉnh</t>
+        </is>
+      </c>
+      <c r="N104" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: hệ thống nhiều cơ sở là lợi thế thật ở đây. Hướng dẫn khách xin bản sao hồ sơ điều trị, phim sau cấy và thông tin hệ trụ để cơ sở mới tiếp nhận.</t>
         </is>
       </c>
       <c r="O104" s="10" t="inlineStr">
@@ -10870,7 +10977,7 @@
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Khách tỉnh &amp; Việt kiều</t>
         </is>
       </c>
     </row>
@@ -10892,13 +10999,17 @@
       </c>
       <c r="D105" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E105" s="28" t="inlineStr"/>
+          <t>nha khoa nào làm implant cho người già</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F105" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G105" s="28" t="inlineStr">
@@ -10923,12 +11034,16 @@
       </c>
       <c r="K105" s="28" t="inlineStr"/>
       <c r="L105" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M105" s="10" t="inlineStr"/>
-      <c r="N105" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M105" s="10" t="inlineStr">
+        <is>
+          <t>implant cho người già ở đâu</t>
+        </is>
+      </c>
+      <c r="N105" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tiêu chí thêm cho người cao tuổi — có phối hợp với bác sĩ nội khoa, có quy trình theo dõi dấu hiệu sinh tồn, lịch hẹn linh hoạt. Dẫn sang cụm C13.</t>
         </is>
       </c>
       <c r="O105" s="10" t="inlineStr">
@@ -10943,7 +11058,7 @@
       </c>
       <c r="Q105" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
     </row>
@@ -10965,18 +11080,22 @@
       </c>
       <c r="D106" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E106" s="28" t="inlineStr"/>
+          <t>giấy phép hoạt động của phòng khám nha khoa tra ở đâu</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G106" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
@@ -10998,10 +11117,14 @@
       <c r="L106" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="M106" s="10" t="inlineStr"/>
-      <c r="N106" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M106" s="10" t="inlineStr">
+        <is>
+          <t>tra giấy phép phòng khám nha khoa</t>
+        </is>
+      </c>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: hướng dẫn khách tra trên cổng thông tin của Sở Y tế địa phương và đối chiếu với bảng hiệu treo tại cơ sở. Nêu rõ số giấy phép phải trùng với pháp nhân ghi trên hợp đồng và hoá đơn.</t>
         </is>
       </c>
       <c r="O106" s="10" t="inlineStr">
@@ -11011,7 +11134,7 @@
       </c>
       <c r="P106" s="10" t="inlineStr">
         <is>
-          <t>R3 · R4 · R6</t>
+          <t>R3 · Đúng pháp nhân</t>
         </is>
       </c>
       <c r="Q106" s="10" t="inlineStr">
@@ -11038,10 +11161,14 @@
       </c>
       <c r="D107" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E107" s="28" t="inlineStr"/>
+          <t>Em mất một răng hàm trong cùng, nhai vẫn bình thường. Có nhất thiết phải trồng implant không hay để vậy cũng được ạ?</t>
+        </is>
+      </c>
+      <c r="E107" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F107" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11049,7 +11176,7 @@
       </c>
       <c r="G107" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H107" s="28" t="inlineStr">
@@ -11069,12 +11196,16 @@
       </c>
       <c r="K107" s="28" t="inlineStr"/>
       <c r="L107" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M107" s="10" t="inlineStr"/>
-      <c r="N107" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M107" s="10" t="inlineStr">
+        <is>
+          <t>có cần trồng răng hàm không</t>
+        </is>
+      </c>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không phải mất răng nào cũng bắt buộc trồng. Răng số 8 (răng khôn) thường KHÔNG cần trồng lại. Nhưng mất răng số 6 hoặc 7 để lâu thì răng bên cạnh nghiêng vào, răng đối diện trồi xuống và xương tiêu — lúc đó chi phí phục hồi cao hơn. Nêu mốc thời gian để khách tự quyết.</t>
         </is>
       </c>
       <c r="O107" s="10" t="inlineStr">
@@ -11111,18 +11242,22 @@
       </c>
       <c r="D108" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E108" s="28" t="inlineStr"/>
+          <t>khi nào không nên cấy implant</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G108" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
@@ -11142,12 +11277,16 @@
       </c>
       <c r="K108" s="28" t="inlineStr"/>
       <c r="L108" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M108" s="10" t="inlineStr"/>
-      <c r="N108" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M108" s="10" t="inlineStr">
+        <is>
+          <t>khi nào không nên cấy implant</t>
+        </is>
+      </c>
+      <c r="N108" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: liệt kê thẳng 7 trường hợp nên cân nhắc phương án khác — đang xạ trị vùng hàm mặt, dùng thuốc chống huỷ xương liều cao, tiểu đường chưa kiểm soát, viêm nha chu toàn hàm chưa điều trị, hút thuốc nhiều chưa sẵn sàng ngưng, trẻ chưa phát triển xong xương hàm, không đủ khả năng theo đuổi tái khám dài hạn.</t>
         </is>
       </c>
       <c r="O108" s="10" t="inlineStr">
@@ -11157,7 +11296,7 @@
       </c>
       <c r="P108" s="10" t="inlineStr">
         <is>
-          <t>R0 · R6</t>
+          <t>R13 · Mời thăm khám, không kết luận thay bác sĩ</t>
         </is>
       </c>
       <c r="Q108" s="10" t="inlineStr">
@@ -11184,18 +11323,22 @@
       </c>
       <c r="D109" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E109" s="28" t="inlineStr"/>
+          <t>cầu răng sứ và implant nên chọn cái nào</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F109" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G109" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H109" s="28" t="inlineStr">
@@ -11215,12 +11358,16 @@
       </c>
       <c r="K109" s="28" t="inlineStr"/>
       <c r="L109" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M109" s="10" t="inlineStr"/>
-      <c r="N109" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M109" s="10" t="inlineStr">
+        <is>
+          <t>cầu răng hay implant</t>
+        </is>
+      </c>
+      <c r="N109" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: bảng so sánh trung thực 5 dòng — xâm lấn răng bên cạnh, thời gian hoàn tất, chi phí ban đầu, chi phí dài hạn, ảnh hưởng tới xương hàm. Nêu rõ cầu răng HỢP HƠN khi hai răng bên cạnh đã có chỉ định bọc sẵn hoặc khách không thể chờ nhiều tháng.</t>
         </is>
       </c>
       <c r="O109" s="10" t="inlineStr">
@@ -11257,10 +11404,14 @@
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E110" s="28" t="inlineStr"/>
+          <t>hàm tháo lắp có còn dùng được không hay lỗi thời rồi</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11268,7 +11419,7 @@
       </c>
       <c r="G110" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
@@ -11288,12 +11439,16 @@
       </c>
       <c r="K110" s="28" t="inlineStr"/>
       <c r="L110" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M110" s="10" t="inlineStr"/>
-      <c r="N110" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M110" s="10" t="inlineStr">
+        <is>
+          <t>hàm tháo lắp hay implant</t>
+        </is>
+      </c>
+      <c r="N110" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không lỗi thời — hàm tháo lắp vẫn là lựa chọn hợp lý khi sức khoẻ không cho phép phẫu thuật, khi ngân sách hạn chế, hoặc làm giải pháp tạm trong lúc chờ. Nêu rõ nhược điểm (lỏng dần do xương tiêu) để khách chọn có hiểu biết.</t>
         </is>
       </c>
       <c r="O110" s="10" t="inlineStr">
@@ -11308,7 +11463,7 @@
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng hàm</t>
+          <t>Mất nhiều răng / toàn hàm</t>
         </is>
       </c>
     </row>
@@ -11330,10 +11485,14 @@
       </c>
       <c r="D111" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E111" s="28" t="inlineStr"/>
+          <t>mất răng số 8 có cần trồng lại không</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F111" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11341,7 +11500,7 @@
       </c>
       <c r="G111" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H111" s="28" t="inlineStr">
@@ -11361,12 +11520,16 @@
       </c>
       <c r="K111" s="28" t="inlineStr"/>
       <c r="L111" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M111" s="10" t="inlineStr"/>
-      <c r="N111" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M111" s="10" t="inlineStr">
+        <is>
+          <t>mất răng khôn có cần trồng</t>
+        </is>
+      </c>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: hầu như không cần — răng số 8 không tham gia nhiều vào ăn nhai và thường được chỉ định nhổ. Đây là ví dụ rõ nhất của việc nói thẳng điều làm mất đơn hàng.</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -11403,18 +11566,22 @@
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E112" s="28" t="inlineStr"/>
+          <t>Bác sĩ tư vấn em cấy 4 trụ nhưng em thấy chỉ mất 2 răng. Như vậy có phải bị tư vấn thừa không ạ?</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
@@ -11434,12 +11601,16 @@
       </c>
       <c r="K112" s="28" t="inlineStr"/>
       <c r="L112" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M112" s="10" t="inlineStr"/>
-      <c r="N112" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M112" s="10" t="inlineStr">
+        <is>
+          <t>bị tư vấn cấy thừa trụ</t>
+        </is>
+      </c>
+      <c r="N112" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: số trụ không phải lúc nào cũng bằng số răng mất — có ca cần thêm trụ để phân tán lực, có ca ít trụ hơn nhờ cầu trên implant. Hướng dẫn khách yêu cầu giải thích TRÊN PHIM vì sao cần số trụ đó, và quyền hỏi ý kiến thứ hai.</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -11449,7 +11620,7 @@
       </c>
       <c r="P112" s="10" t="inlineStr">
         <is>
-          <t>R0 · R6</t>
+          <t>R6 · Không quy kết nơi tư vấn; R13 không kết luận thay</t>
         </is>
       </c>
       <c r="Q112" s="10" t="inlineStr">
@@ -11476,10 +11647,14 @@
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E113" s="28" t="inlineStr"/>
+          <t>có nên cấy implant khi còn trẻ không</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11509,10 +11684,14 @@
       <c r="L113" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M113" s="10" t="inlineStr"/>
-      <c r="N113" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M113" s="10" t="inlineStr">
+        <is>
+          <t>implant cho người trẻ</t>
+        </is>
+      </c>
+      <c r="N113" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cần chờ xương hàm phát triển xong (thường sau 18–20 tuổi, có ca muộn hơn) vì cấy sớm thì trụ không di chuyển theo xương, gây lệch so với răng thật. Đánh giá bằng phim, không theo tuổi đơn thuần.</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -11549,18 +11728,22 @@
       </c>
       <c r="D114" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E114" s="28" t="inlineStr"/>
+          <t>mất răng lâu năm rồi còn trồng implant được không</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G114" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
@@ -11580,12 +11763,16 @@
       </c>
       <c r="K114" s="28" t="inlineStr"/>
       <c r="L114" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M114" s="10" t="inlineStr"/>
-      <c r="N114" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M114" s="10" t="inlineStr">
+        <is>
+          <t>mất răng lâu năm trồng implant</t>
+        </is>
+      </c>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phần lớn vẫn làm được nhưng thường phải ghép xương hoặc nâng xoang vì xương đã tiêu. Nêu rõ: mất càng lâu thì thủ thuật càng nhiều và chi phí càng tăng — đây là thông tin khách cần để quyết sớm.</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -11600,7 +11787,7 @@
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng hàm</t>
+          <t>Mất răng lâu năm – tiêu xương</t>
         </is>
       </c>
     </row>
@@ -11622,10 +11809,14 @@
       </c>
       <c r="D115" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E115" s="28" t="inlineStr"/>
+          <t>chỉ mất một răng cửa có nên làm implant không</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11633,7 +11824,7 @@
       </c>
       <c r="G115" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
@@ -11653,12 +11844,16 @@
       </c>
       <c r="K115" s="28" t="inlineStr"/>
       <c r="L115" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M115" s="10" t="inlineStr"/>
-      <c r="N115" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M115" s="10" t="inlineStr">
+        <is>
+          <t>implant răng cửa</t>
+        </is>
+      </c>
+      <c r="N115" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: implant là lựa chọn tốt vì không phải mài hai răng cửa bên cạnh — nhưng vùng răng cửa khó về thẩm mỹ (đường viền lợi, màu mão) và cần bác sĩ có kinh nghiệm vùng này. Nêu rõ rủi ro tụt lợi lộ cổ trụ.</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -11673,7 +11868,7 @@
       </c>
       <c r="Q115" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng hàm</t>
+          <t>Mất 1 răng cửa</t>
         </is>
       </c>
     </row>
@@ -11695,18 +11890,22 @@
       </c>
       <c r="D116" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E116" s="28" t="inlineStr"/>
+          <t>đang điều trị nha chu có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F116" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G116" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
@@ -11726,12 +11925,16 @@
       </c>
       <c r="K116" s="28" t="inlineStr"/>
       <c r="L116" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M116" s="10" t="inlineStr"/>
-      <c r="N116" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>nha chu và implant</t>
+        </is>
+      </c>
+      <c r="N116" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phải điều trị ổn định nha chu TRƯỚC khi cấy — vi khuẩn nha chu là nguyên nhân hàng đầu của viêm quanh trụ sau này. Cấy khi nha chu còn hoạt động là đặt trụ vào môi trường nhiễm khuẩn.</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -11768,10 +11971,14 @@
       </c>
       <c r="D117" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E117" s="28" t="inlineStr"/>
+          <t>implant có phải là lựa chọn duy nhất khi mất răng không</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F117" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11779,7 +11986,7 @@
       </c>
       <c r="G117" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
@@ -11799,12 +12006,16 @@
       </c>
       <c r="K117" s="28" t="inlineStr"/>
       <c r="L117" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M117" s="10" t="inlineStr"/>
-      <c r="N117" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M117" s="10" t="inlineStr">
+        <is>
+          <t>các phương án thay răng mất</t>
+        </is>
+      </c>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có 3 nhóm phương án — implant, cầu răng, hàm tháo lắp; mỗi nhóm có chỉ định riêng. Trình bày dạng cây quyết định theo số răng mất và tình trạng răng bên cạnh.</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -11841,10 +12052,14 @@
       </c>
       <c r="D118" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E118" s="28" t="inlineStr"/>
+          <t>nên trồng implant trước hay niềng răng trước</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F118" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11874,10 +12089,14 @@
       <c r="L118" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M118" s="10" t="inlineStr"/>
-      <c r="N118" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>niềng trước hay implant trước</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường niềng trước rồi mới cấy, vì trụ implant KHÔNG di chuyển được bằng khí cụ chỉnh nha. Cấy trước rồi niềng có thể khoá mất khoảng cần dịch chuyển. Quyết định trên kế hoạch toàn hàm.</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -11914,10 +12133,14 @@
       </c>
       <c r="D119" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E119" s="28" t="inlineStr"/>
+          <t>trồng implant có làm được ngay sau khi nhổ răng không</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F119" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -11925,7 +12148,7 @@
       </c>
       <c r="G119" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H119" s="28" t="inlineStr">
@@ -11945,12 +12168,16 @@
       </c>
       <c r="K119" s="28" t="inlineStr"/>
       <c r="L119" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M119" s="10" t="inlineStr"/>
-      <c r="N119" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>cấy implant tức thì</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cấy tức thì làm được trong một số ca có xương tốt và không nhiễm trùng, rút ngắn thời gian đáng kể. Nhưng đây là chỉ định HẸP — không phải ai cũng phù hợp, và cấy tức thì sai chỉ định làm tăng nguy cơ thất bại.</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -11987,18 +12214,22 @@
       </c>
       <c r="D120" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E120" s="28" t="inlineStr"/>
+          <t>người bị loãng xương có nên cấy implant không</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F120" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G120" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H120" s="28" t="inlineStr">
@@ -12018,12 +12249,16 @@
       </c>
       <c r="K120" s="28" t="inlineStr"/>
       <c r="L120" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M120" s="10" t="inlineStr"/>
-      <c r="N120" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>loãng xương và implant</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: loãng xương không phải chống chỉ định tuyệt đối; vấn đề nằm ở THUỐC chống huỷ xương (nhất là đường tiêm) do nguy cơ hoại tử xương hàm. Bắt buộc khai báo thuốc đang dùng và phối hợp với bác sĩ điều trị.</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -12038,7 +12273,7 @@
       </c>
       <c r="Q120" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng hàm</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
     </row>
@@ -12060,10 +12295,14 @@
       </c>
       <c r="D121" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E121" s="28" t="inlineStr"/>
+          <t>không đủ tiền làm implant thì có cách nào khác không</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F121" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12071,7 +12310,7 @@
       </c>
       <c r="G121" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H121" s="28" t="inlineStr">
@@ -12091,12 +12330,16 @@
       </c>
       <c r="K121" s="28" t="inlineStr"/>
       <c r="L121" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M121" s="10" t="inlineStr"/>
-      <c r="N121" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>giải pháp thay thế implant</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nêu thẳng các phương án chi phí thấp hơn và điều kiện áp dụng, kèm cảnh báo trung thực về tuổi thọ và nhược điểm từng phương án. Không ép khách chọn implant.</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -12133,10 +12376,14 @@
       </c>
       <c r="D122" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E122" s="28" t="inlineStr"/>
+          <t>mất răng có ảnh hưởng gì nếu không trồng lại</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F122" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12144,7 +12391,7 @@
       </c>
       <c r="G122" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H122" s="28" t="inlineStr">
@@ -12164,12 +12411,16 @@
       </c>
       <c r="K122" s="28" t="inlineStr"/>
       <c r="L122" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M122" s="10" t="inlineStr"/>
-      <c r="N122" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>không trồng lại răng mất</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 4 hệ quả theo thời gian — răng bên cạnh nghiêng, răng đối diện trồi, lệch khớp cắn, tiêu xương vùng mất răng. Nêu mốc thời gian tương đối để khách tự cân nhắc, không doạ.</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -12206,18 +12457,22 @@
       </c>
       <c r="D123" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E123" s="28" t="inlineStr"/>
+          <t>có nên cấy implant cả hàm khi chỉ hỏng vài răng</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F123" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G123" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H123" s="28" t="inlineStr">
@@ -12237,12 +12492,16 @@
       </c>
       <c r="K123" s="28" t="inlineStr"/>
       <c r="L123" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M123" s="10" t="inlineStr"/>
-      <c r="N123" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>cấy implant cả hàm hay từng răng</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không nên mặc định làm cả hàm. Nêu tiêu chí: răng còn lại có giữ được không (nha chu, chân răng), khớp cắn tổng thể, chi phí dài hạn. Giữ được răng thật luôn là ưu tiên.</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -12257,7 +12516,7 @@
       </c>
       <c r="Q123" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng hàm</t>
+          <t>Mất nhiều răng / toàn hàm</t>
         </is>
       </c>
     </row>
@@ -12279,10 +12538,14 @@
       </c>
       <c r="D124" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E124" s="28" t="inlineStr"/>
+          <t>chụp CT Conebeam để làm gì khi trồng implant</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F124" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12290,7 +12553,7 @@
       </c>
       <c r="G124" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H124" s="28" t="inlineStr">
@@ -12310,12 +12573,16 @@
       </c>
       <c r="K124" s="28" t="inlineStr"/>
       <c r="L124" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M124" s="10" t="inlineStr"/>
-      <c r="N124" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>CT Conebeam implant</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: CT Conebeam cho ảnh 3 chiều để đo 3 thứ mà phim thường không đo được — chiều cao và bề rộng xương, khoảng cách tới ống thần kinh răng dưới, chiều cao xương dưới xoang hàm trên. Không có phim này thì không thể lên kế hoạch cấy chính xác.</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -12352,18 +12619,22 @@
       </c>
       <c r="D125" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E125" s="28" t="inlineStr"/>
+          <t>ghép xương trong cấy implant là gì có đau không</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F125" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G125" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H125" s="28" t="inlineStr">
@@ -12383,12 +12654,16 @@
       </c>
       <c r="K125" s="28" t="inlineStr"/>
       <c r="L125" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M125" s="10" t="inlineStr"/>
-      <c r="N125" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>ghép xương implant</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: ghép xương là bù thêm thể tích xương để đủ ôm trụ. Mức độ khó chịu tương đương hoặc hơn cấy trụ đơn thuần một chút, kiểm soát được bằng thuốc. Nêu rõ ghép xương kéo dài tổng thời gian điều trị thêm 4–6 tháng.</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -12425,18 +12700,22 @@
       </c>
       <c r="D126" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E126" s="28" t="inlineStr"/>
+          <t>Bác sĩ bảo em phải nâng xoang mới cấy được. Nâng xoang có nguy hiểm không ạ?</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F126" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G126" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H126" s="28" t="inlineStr">
@@ -12456,12 +12735,16 @@
       </c>
       <c r="K126" s="28" t="inlineStr"/>
       <c r="L126" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M126" s="10" t="inlineStr"/>
-      <c r="N126" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>nâng xoang có nguy hiểm không</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nâng xoang là thủ thuật thường quy khi xương hàm trên vùng sau không đủ cao. Rủi ro chính là rách màng xoang — xử lý được ngay trong mổ nếu phát hiện. Phân biệt nâng xoang kín (ít xâm lấn) và nâng xoang hở (ca thiếu xương nhiều).</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -12498,10 +12781,14 @@
       </c>
       <c r="D127" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E127" s="28" t="inlineStr"/>
+          <t>kế hoạch điều trị implant gồm những bước nào</t>
+        </is>
+      </c>
+      <c r="E127" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F127" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12509,7 +12796,7 @@
       </c>
       <c r="G127" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H127" s="28" t="inlineStr">
@@ -12529,12 +12816,16 @@
       </c>
       <c r="K127" s="28" t="inlineStr"/>
       <c r="L127" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M127" s="10" t="inlineStr"/>
-      <c r="N127" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>kế hoạch điều trị implant</t>
+        </is>
+      </c>
+      <c r="N127" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 5 bước — khám và chụp CT, lập kế hoạch và báo giá bằng văn bản, cấy trụ, chờ tích hợp, phục hình mão. Nhấn: báo giá phải đến SAU khi có phim, không phải trước.</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -12571,10 +12862,14 @@
       </c>
       <c r="D128" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E128" s="28" t="inlineStr"/>
+          <t>có cần xét nghiệm máu trước khi cấy implant không</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F128" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12582,7 +12877,7 @@
       </c>
       <c r="G128" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H128" s="28" t="inlineStr">
@@ -12602,12 +12897,16 @@
       </c>
       <c r="K128" s="28" t="inlineStr"/>
       <c r="L128" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M128" s="10" t="inlineStr"/>
-      <c r="N128" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>xét nghiệm trước cấy implant</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường có chỉ định xét nghiệm cơ bản để đánh giá đông máu, đường huyết và tình trạng nhiễm trùng, nhất là với người có bệnh nền. Chỉ định cụ thể do bác sĩ quyết sau khám.</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -12617,7 +12916,7 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R13 · Không chỉ định thay bác sĩ</t>
         </is>
       </c>
       <c r="Q128" s="10" t="inlineStr">
@@ -12644,18 +12943,22 @@
       </c>
       <c r="D129" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E129" s="28" t="inlineStr"/>
+          <t>xương hàm mỏng có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E129" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F129" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G129" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H129" s="28" t="inlineStr">
@@ -12675,12 +12978,16 @@
       </c>
       <c r="K129" s="28" t="inlineStr"/>
       <c r="L129" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M129" s="10" t="inlineStr"/>
-      <c r="N129" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>xương hàm mỏng cấy implant</t>
+        </is>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường vẫn làm được sau khi ghép xương hoặc chọn trụ kích thước phù hợp. Mức độ mỏng đo trên CT quyết định hướng xử lý. Không kết luận qua mô tả hay qua ảnh chụp miệng.</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -12690,7 +12997,7 @@
       </c>
       <c r="P129" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R13 · Phải có phim</t>
         </is>
       </c>
       <c r="Q129" s="10" t="inlineStr">
@@ -12717,10 +13024,14 @@
       </c>
       <c r="D130" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E130" s="28" t="inlineStr"/>
+          <t>phim X-quang thường có đủ để cấy implant không</t>
+        </is>
+      </c>
+      <c r="E130" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F130" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12728,7 +13039,7 @@
       </c>
       <c r="G130" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
@@ -12748,12 +13059,16 @@
       </c>
       <c r="K130" s="28" t="inlineStr"/>
       <c r="L130" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M130" s="10" t="inlineStr"/>
-      <c r="N130" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>phim thường hay CT cho implant</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phim toàn cảnh chỉ cho ảnh 2 chiều, không đo được bề rộng xương và dễ sai lệch tỷ lệ. Cấy dựa trên phim thường làm tăng nguy cơ chạm thần kinh và thủng xoang. CT Conebeam là chuẩn cho lập kế hoạch.</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -12790,10 +13105,14 @@
       </c>
       <c r="D131" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E131" s="28" t="inlineStr"/>
+          <t>máng hướng dẫn phẫu thuật implant là gì</t>
+        </is>
+      </c>
+      <c r="E131" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F131" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12823,10 +13142,14 @@
       <c r="L131" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M131" s="10" t="inlineStr"/>
-      <c r="N131" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>máng hướng dẫn phẫu thuật</t>
+        </is>
+      </c>
+      <c r="N131" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là khí cụ chế tạo từ dữ liệu CT giúp đặt trụ đúng vị trí và góc đã lên kế hoạch. Tăng độ chính xác, hữu ích ở ca nhiều trụ hoặc vùng giải phẫu khó; không bắt buộc cho mọi ca.</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -12863,10 +13186,14 @@
       </c>
       <c r="D132" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E132" s="28" t="inlineStr"/>
+          <t>sau khi chụp CT bao lâu thì cấy được</t>
+        </is>
+      </c>
+      <c r="E132" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F132" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -12896,10 +13223,14 @@
       <c r="L132" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M132" s="10" t="inlineStr"/>
-      <c r="N132" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M132" s="10" t="inlineStr">
+        <is>
+          <t>sau chụp CT bao lâu cấy implant</t>
+        </is>
+      </c>
+      <c r="N132" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường cấy được ngay sau khi có kế hoạch nếu không cần xử lý gì thêm. Có ca phải điều trị nha chu hoặc nhổ răng và chờ lành trước.</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -12936,18 +13267,22 @@
       </c>
       <c r="D133" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E133" s="28" t="inlineStr"/>
+          <t>Em đi 3 nơi thì 3 nơi đưa 3 kế hoạch khác nhau, nơi bảo ghép xương nơi bảo không. Em nên tin ai ạ?</t>
+        </is>
+      </c>
+      <c r="E133" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F133" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G133" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H133" s="28" t="inlineStr">
@@ -12967,12 +13302,16 @@
       </c>
       <c r="K133" s="28" t="inlineStr"/>
       <c r="L133" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M133" s="10" t="inlineStr"/>
-      <c r="N133" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M133" s="10" t="inlineStr">
+        <is>
+          <t>nhiều kế hoạch điều trị khác nhau</t>
+        </is>
+      </c>
+      <c r="N133" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khác biệt kế hoạch là chuyện bình thường vì phụ thuộc trường phái và thiết bị. Hướng dẫn khách so sánh trên CÙNG MỘT CƠ SỞ DỮ LIỆU: yêu cầu mỗi nơi chỉ trên phim vì sao cần/không cần ghép xương. Không đánh giá nơi nào đúng.</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -12982,7 +13321,7 @@
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R6 · Không phán xét; R13 không kết luận thay</t>
         </is>
       </c>
       <c r="Q133" s="10" t="inlineStr">
@@ -13009,10 +13348,14 @@
       </c>
       <c r="D134" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E134" s="28" t="inlineStr"/>
+          <t>khớp cắn có ảnh hưởng đến implant không</t>
+        </is>
+      </c>
+      <c r="E134" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F134" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13042,10 +13385,14 @@
       <c r="L134" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M134" s="10" t="inlineStr"/>
-      <c r="N134" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>khớp cắn và implant</t>
+        </is>
+      </c>
+      <c r="N134" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có — trụ implant không có dây chằng nha chu nên không 'đệm' lực như răng thật. Khớp cắn sai gây quá tải, dẫn tới vỡ mão, gãy vít và tiêu xương quanh trụ. Chỉnh khớp cắn là bước bắt buộc khi phục hình.</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -13082,10 +13429,14 @@
       </c>
       <c r="D135" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E135" s="28" t="inlineStr"/>
+          <t>cần nhổ răng trước khi cấy implant bao lâu</t>
+        </is>
+      </c>
+      <c r="E135" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F135" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13093,7 +13444,7 @@
       </c>
       <c r="G135" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H135" s="28" t="inlineStr">
@@ -13113,12 +13464,16 @@
       </c>
       <c r="K135" s="28" t="inlineStr"/>
       <c r="L135" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M135" s="10" t="inlineStr"/>
-      <c r="N135" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M135" s="10" t="inlineStr">
+        <is>
+          <t>nhổ răng trước khi cấy implant</t>
+        </is>
+      </c>
+      <c r="N135" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường chờ 2–3 tháng cho ổ răng lành nếu không cấy tức thì. Ca nhiễm trùng nặng chờ lâu hơn. Dải thời gian, không mốc cứng.</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -13128,7 +13483,7 @@
       </c>
       <c r="P135" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R13 · Nêu dải</t>
         </is>
       </c>
       <c r="Q135" s="10" t="inlineStr">
@@ -13155,10 +13510,14 @@
       </c>
       <c r="D136" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E136" s="28" t="inlineStr"/>
+          <t>đo mật độ xương hàm để làm gì</t>
+        </is>
+      </c>
+      <c r="E136" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F136" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13188,10 +13547,14 @@
       <c r="L136" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M136" s="10" t="inlineStr"/>
-      <c r="N136" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>mật độ xương hàm implant</t>
+        </is>
+      </c>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: mật độ xương quyết định độ vững ban đầu của trụ và thời gian chờ tích hợp. Xương mềm thì chờ lâu hơn và có thể cần kỹ thuật đặt trụ khác.</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -13228,10 +13591,14 @@
       </c>
       <c r="D137" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E137" s="28" t="inlineStr"/>
+          <t>lấy dấu răng để làm mão implant có khó chịu không</t>
+        </is>
+      </c>
+      <c r="E137" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F137" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13239,7 +13606,7 @@
       </c>
       <c r="G137" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H137" s="28" t="inlineStr">
@@ -13259,12 +13626,16 @@
       </c>
       <c r="K137" s="28" t="inlineStr"/>
       <c r="L137" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M137" s="10" t="inlineStr"/>
-      <c r="N137" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M137" s="10" t="inlineStr">
+        <is>
+          <t>lấy dấu răng implant</t>
+        </is>
+      </c>
+      <c r="N137" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: lấy dấu bằng vật liệu truyền thống có thể hơi khó chịu với người nhạy cảm phản xạ nôn; nhiều cơ sở dùng máy quét trong miệng nên nhẹ nhàng hơn. Chỉ nêu thiết bị cơ sở thực sự có.</t>
         </is>
       </c>
       <c r="O137" s="10" t="inlineStr">
@@ -13274,7 +13645,7 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R7 · Chỉ nêu thiết bị cơ sở đang có</t>
         </is>
       </c>
       <c r="Q137" s="10" t="inlineStr">
@@ -13301,18 +13672,22 @@
       </c>
       <c r="D138" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E138" s="28" t="inlineStr"/>
+          <t>kế hoạch điều trị implant có được đưa bằng văn bản không</t>
+        </is>
+      </c>
+      <c r="E138" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F138" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G138" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H138" s="28" t="inlineStr">
@@ -13332,12 +13707,16 @@
       </c>
       <c r="K138" s="28" t="inlineStr"/>
       <c r="L138" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M138" s="10" t="inlineStr"/>
-      <c r="N138" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>kế hoạch điều trị bằng văn bản</t>
+        </is>
+      </c>
+      <c r="N138" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nên và cần — văn bản phải ghi số trụ, hãng trụ, có ghép xương hay không, tổng thời gian dự kiến và báo giá tách 3 cấu phần. Đây là cách tự bảo vệ tốt nhất của khách.</t>
         </is>
       </c>
       <c r="O138" s="10" t="inlineStr">
@@ -13347,7 +13726,7 @@
       </c>
       <c r="P138" s="10" t="inlineStr">
         <is>
-          <t>R13 · R2</t>
+          <t>R12 · Không ghi số giá trong bài</t>
         </is>
       </c>
       <c r="Q138" s="10" t="inlineStr">
@@ -13374,10 +13753,14 @@
       </c>
       <c r="D139" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E139" s="28" t="inlineStr"/>
+          <t>chụp CT Conebeam có hại không</t>
+        </is>
+      </c>
+      <c r="E139" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F139" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13407,10 +13790,14 @@
       <c r="L139" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M139" s="10" t="inlineStr"/>
-      <c r="N139" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M139" s="10" t="inlineStr">
+        <is>
+          <t>CT Conebeam có hại không</t>
+        </is>
+      </c>
+      <c r="N139" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: liều tia của CT Conebeam nha khoa thấp hơn nhiều so với CT y khoa toàn thân, và chỉ chụp khi có chỉ định. Phụ nữ mang thai cần thông báo trước.</t>
         </is>
       </c>
       <c r="O139" s="10" t="inlineStr">
@@ -13447,10 +13834,14 @@
       </c>
       <c r="D140" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E140" s="28" t="inlineStr"/>
+          <t>có thể dùng phim chụp ở nơi khác được không</t>
+        </is>
+      </c>
+      <c r="E140" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F140" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -13480,10 +13871,14 @@
       <c r="L140" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M140" s="10" t="inlineStr"/>
-      <c r="N140" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M140" s="10" t="inlineStr">
+        <is>
+          <t>dùng phim CT nơi khác</t>
+        </is>
+      </c>
+      <c r="N140" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dùng được nếu phim còn mới và đủ trường chụp vùng cần cấy; nên mang theo file gốc (DICOM) chứ không chỉ ảnh in. Có ca vẫn phải chụp lại vì tình trạng đã thay đổi.</t>
         </is>
       </c>
       <c r="O140" s="10" t="inlineStr">
@@ -13520,10 +13915,14 @@
       </c>
       <c r="D141" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E141" s="28" t="inlineStr"/>
+          <t>trồng răng implant mất bao lâu</t>
+        </is>
+      </c>
+      <c r="E141" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F141" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13531,7 +13930,7 @@
       </c>
       <c r="G141" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H141" s="28" t="inlineStr">
@@ -13551,12 +13950,16 @@
       </c>
       <c r="K141" s="28" t="inlineStr"/>
       <c r="L141" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M141" s="10" t="inlineStr"/>
-      <c r="N141" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M141" s="10" t="inlineStr">
+        <is>
+          <t>trồng implant mất bao lâu</t>
+        </is>
+      </c>
+      <c r="N141" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tổng thường 3–6 tháng cho ca không ghép xương, 6–12 tháng nếu có ghép. Chia 3 mốc: cấy trụ (1 buổi), chờ tích hợp (3–6 tháng), phục hình mão (2–3 buổi). Nêu DẢI, không hứa mốc cứng.</t>
         </is>
       </c>
       <c r="O141" s="10" t="inlineStr">
@@ -13566,7 +13969,7 @@
       </c>
       <c r="P141" s="10" t="inlineStr">
         <is>
-          <t>R13 · R1</t>
+          <t>R13 · Không hứa thời gian cứng</t>
         </is>
       </c>
       <c r="Q141" s="10" t="inlineStr">
@@ -13593,10 +13996,14 @@
       </c>
       <c r="D142" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E142" s="28" t="inlineStr"/>
+          <t>cấy implant mất mấy buổi</t>
+        </is>
+      </c>
+      <c r="E142" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F142" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13604,7 +14011,7 @@
       </c>
       <c r="G142" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H142" s="28" t="inlineStr">
@@ -13624,12 +14031,16 @@
       </c>
       <c r="K142" s="28" t="inlineStr"/>
       <c r="L142" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M142" s="10" t="inlineStr"/>
-      <c r="N142" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M142" s="10" t="inlineStr">
+        <is>
+          <t>cấy implant mấy buổi</t>
+        </is>
+      </c>
+      <c r="N142" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường 4–6 buổi — khám và chụp CT, cấy trụ, cắt chỉ/kiểm tra, lấy dấu, thử sườn, gắn mão. Ca ghép xương thêm 1–2 buổi. Liệt kê rõ để khách sắp lịch nghỉ làm.</t>
         </is>
       </c>
       <c r="O142" s="10" t="inlineStr">
@@ -13666,10 +14077,14 @@
       </c>
       <c r="D143" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E143" s="28" t="inlineStr"/>
+          <t>Trong mấy tháng chờ tích hợp xương thì chỗ mất răng trông thế nào, em có răng để ăn không ạ?</t>
+        </is>
+      </c>
+      <c r="E143" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F143" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13677,7 +14092,7 @@
       </c>
       <c r="G143" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H143" s="28" t="inlineStr">
@@ -13697,12 +14112,16 @@
       </c>
       <c r="K143" s="28" t="inlineStr"/>
       <c r="L143" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M143" s="10" t="inlineStr"/>
-      <c r="N143" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M143" s="10" t="inlineStr">
+        <is>
+          <t>răng tạm khi chờ implant</t>
+        </is>
+      </c>
+      <c r="N143" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có phương án răng tạm — hàm tháo lắp tạm, cầu dán tạm hoặc mão tạm trên trụ ở ca đủ điều kiện. Vùng răng cửa gần như luôn có răng tạm vì lý do thẩm mỹ. Hỏi rõ phương án tạm ngay từ buổi lập kế hoạch.</t>
         </is>
       </c>
       <c r="O143" s="10" t="inlineStr">
@@ -13739,10 +14158,14 @@
       </c>
       <c r="D144" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E144" s="28" t="inlineStr"/>
+          <t>cấy implant xong bao lâu thì ăn uống bình thường</t>
+        </is>
+      </c>
+      <c r="E144" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F144" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13750,7 +14173,7 @@
       </c>
       <c r="G144" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H144" s="28" t="inlineStr">
@@ -13770,12 +14193,16 @@
       </c>
       <c r="K144" s="28" t="inlineStr"/>
       <c r="L144" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M144" s="10" t="inlineStr"/>
-      <c r="N144" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>sau cấy implant bao lâu ăn được</t>
+        </is>
+      </c>
+      <c r="N144" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: ăn mềm ngay trong ngày, nhai bên đối diện 1–2 tuần, ăn nhai bình thường trên trụ chỉ sau khi đã gắn mão và bác sĩ cho phép. Nhai sớm trên trụ chưa tích hợp là nguyên nhân thất bại thường gặp.</t>
         </is>
       </c>
       <c r="O144" s="10" t="inlineStr">
@@ -13812,10 +14239,14 @@
       </c>
       <c r="D145" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E145" s="28" t="inlineStr"/>
+          <t>cấy implant có phải nghỉ làm không</t>
+        </is>
+      </c>
+      <c r="E145" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F145" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13823,7 +14254,7 @@
       </c>
       <c r="G145" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H145" s="28" t="inlineStr">
@@ -13843,12 +14274,16 @@
       </c>
       <c r="K145" s="28" t="inlineStr"/>
       <c r="L145" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M145" s="10" t="inlineStr"/>
-      <c r="N145" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M145" s="10" t="inlineStr">
+        <is>
+          <t>cấy implant nghỉ làm mấy ngày</t>
+        </is>
+      </c>
+      <c r="N145" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phần lớn ca 1 trụ quay lại làm việc sau 1–2 ngày. Ca nhiều trụ hoặc ghép xương lớn nên thu xếp 3–5 ngày. Tránh lên lịch ngay trước sự kiện quan trọng.</t>
         </is>
       </c>
       <c r="O145" s="10" t="inlineStr">
@@ -13885,18 +14320,22 @@
       </c>
       <c r="D146" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E146" s="28" t="inlineStr"/>
+          <t>quy trình cấy implant diễn ra như thế nào</t>
+        </is>
+      </c>
+      <c r="E146" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F146" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G146" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H146" s="28" t="inlineStr">
@@ -13918,10 +14357,14 @@
       <c r="L146" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="M146" s="10" t="inlineStr"/>
-      <c r="N146" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M146" s="10" t="inlineStr">
+        <is>
+          <t>quy trình cấy implant</t>
+        </is>
+      </c>
+      <c r="N146" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: mô tả theo trình tự trong buổi cấy — gây tê, rạch lợi, khoan tạo lỗ theo kế hoạch trên CT, đặt trụ, khâu đóng. Thời gian thực tế cho 1 trụ thường 30–60 phút. Tránh mô tả gây sợ, không dùng ảnh cận cảnh dụng cụ.</t>
         </is>
       </c>
       <c r="O146" s="10" t="inlineStr">
@@ -13958,10 +14401,14 @@
       </c>
       <c r="D147" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E147" s="28" t="inlineStr"/>
+          <t>khách ở tỉnh làm implant phải lên mấy lần</t>
+        </is>
+      </c>
+      <c r="E147" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F147" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -13969,7 +14416,7 @@
       </c>
       <c r="G147" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H147" s="28" t="inlineStr">
@@ -13989,12 +14436,16 @@
       </c>
       <c r="K147" s="28" t="inlineStr"/>
       <c r="L147" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M147" s="10" t="inlineStr"/>
-      <c r="N147" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>khách tỉnh làm implant mấy lần</t>
+        </is>
+      </c>
+      <c r="N147" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: gom được còn 3–4 lần nếu lên kế hoạch từ đầu — kết hợp khám và cấy trong một chuyến, gộp buổi lấy dấu và thử sườn. Nêu phương án tái khám tại cơ sở gần nhất trong hệ thống.</t>
         </is>
       </c>
       <c r="O147" s="10" t="inlineStr">
@@ -14009,7 +14460,7 @@
       </c>
       <c r="Q147" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng cửa</t>
+          <t>Khách tỉnh &amp; Việt kiều</t>
         </is>
       </c>
     </row>
@@ -14031,13 +14482,17 @@
       </c>
       <c r="D148" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E148" s="28" t="inlineStr"/>
+          <t>cắt chỉ sau cấy implant khi nào</t>
+        </is>
+      </c>
+      <c r="E148" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F148" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="G148" s="28" t="inlineStr">
@@ -14062,12 +14517,16 @@
       </c>
       <c r="K148" s="28" t="inlineStr"/>
       <c r="L148" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M148" s="10" t="inlineStr"/>
-      <c r="N148" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>cắt chỉ sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N148" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường 7–10 ngày sau cấy. Một số cơ sở dùng chỉ tự tiêu nên không cần cắt. Hỏi rõ trước khi ra về.</t>
         </is>
       </c>
       <c r="O148" s="10" t="inlineStr">
@@ -14104,18 +14563,22 @@
       </c>
       <c r="D149" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E149" s="28" t="inlineStr"/>
+          <t>cấy implant có cần gây mê không</t>
+        </is>
+      </c>
+      <c r="E149" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G149" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H149" s="28" t="inlineStr">
@@ -14137,10 +14600,14 @@
       <c r="L149" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="M149" s="10" t="inlineStr"/>
-      <c r="N149" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M149" s="10" t="inlineStr">
+        <is>
+          <t>gây mê khi cấy implant</t>
+        </is>
+      </c>
+      <c r="N149" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phần lớn ca chỉ cần gây tê tại chỗ. An thần hoặc gây mê cân nhắc với ca nhiều trụ, ca kéo dài hoặc người quá lo lắng — và phải có điều kiện theo dõi tương ứng.</t>
         </is>
       </c>
       <c r="O149" s="10" t="inlineStr">
@@ -14177,10 +14644,14 @@
       </c>
       <c r="D150" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E150" s="28" t="inlineStr"/>
+          <t>Em muốn làm xong trước Tết, giờ còn 3 tháng thì có kịp không ạ?</t>
+        </is>
+      </c>
+      <c r="E150" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F150" s="28" t="inlineStr">
         <is>
           <t>Hot</t>
@@ -14188,7 +14659,7 @@
       </c>
       <c r="G150" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H150" s="28" t="inlineStr">
@@ -14208,12 +14679,16 @@
       </c>
       <c r="K150" s="28" t="inlineStr"/>
       <c r="L150" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M150" s="10" t="inlineStr"/>
-      <c r="N150" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>làm implant có kịp không</t>
+        </is>
+      </c>
+      <c r="N150" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 3 tháng đủ cho ca xương tốt không ghép, nhưng không đủ nếu phải ghép xương hay nâng xoang. Gợi ý: khám và chụp CT sớm để biết chính xác; nếu không kịp thì có phương án răng tạm cho dịp lễ.</t>
         </is>
       </c>
       <c r="O150" s="10" t="inlineStr">
@@ -14223,7 +14698,7 @@
       </c>
       <c r="P150" s="10" t="inlineStr">
         <is>
-          <t>R13 · R1</t>
+          <t>R13 · Không hứa mốc cứng</t>
         </is>
       </c>
       <c r="Q150" s="10" t="inlineStr">
@@ -14250,13 +14725,17 @@
       </c>
       <c r="D151" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E151" s="28" t="inlineStr"/>
+          <t>lắp mão sứ lên implant mất bao lâu</t>
+        </is>
+      </c>
+      <c r="E151" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G151" s="28" t="inlineStr">
@@ -14281,12 +14760,16 @@
       </c>
       <c r="K151" s="28" t="inlineStr"/>
       <c r="L151" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M151" s="10" t="inlineStr"/>
-      <c r="N151" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>lắp mão implant bao lâu</t>
+        </is>
+      </c>
+      <c r="N151" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường 2–3 buổi trong 1–2 tuần — lấy dấu, thử sườn/thử màu, gắn chính thức. Vùng răng cửa có thể thêm buổi chỉnh thẩm mỹ.</t>
         </is>
       </c>
       <c r="O151" s="10" t="inlineStr">
@@ -14323,13 +14806,17 @@
       </c>
       <c r="D152" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E152" s="28" t="inlineStr"/>
+          <t>sau cấy implant có phải tái khám nhiều không</t>
+        </is>
+      </c>
+      <c r="E152" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F152" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="G152" s="28" t="inlineStr">
@@ -14354,12 +14841,16 @@
       </c>
       <c r="K152" s="28" t="inlineStr"/>
       <c r="L152" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M152" s="10" t="inlineStr"/>
-      <c r="N152" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>tái khám sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N152" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dày trong năm đầu (sau cấy, cắt chỉ, trước phục hình, sau gắn mão), sau đó 6–12 tháng một lần. Bỏ tái khám là điều kiện loại trừ bảo hành thường gặp.</t>
         </is>
       </c>
       <c r="O152" s="10" t="inlineStr">
@@ -14396,13 +14887,17 @@
       </c>
       <c r="D153" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E153" s="28" t="inlineStr"/>
+          <t>cấy nhiều trụ cùng lúc được không</t>
+        </is>
+      </c>
+      <c r="E153" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G153" s="28" t="inlineStr">
@@ -14427,12 +14922,16 @@
       </c>
       <c r="K153" s="28" t="inlineStr"/>
       <c r="L153" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M153" s="10" t="inlineStr"/>
-      <c r="N153" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>cấy nhiều trụ cùng lúc</t>
+        </is>
+      </c>
+      <c r="N153" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: được và thường làm để giảm số lần phẫu thuật, nhưng phụ thuộc sức khoẻ toàn thân và thời gian ngồi ghế. Bác sĩ cân nhắc chia đợt với người lớn tuổi.</t>
         </is>
       </c>
       <c r="O153" s="10" t="inlineStr">
@@ -14447,7 +14946,7 @@
       </c>
       <c r="Q153" s="10" t="inlineStr">
         <is>
-          <t>Mất 1 răng cửa</t>
+          <t>Mất nhiều răng / toàn hàm</t>
         </is>
       </c>
     </row>
@@ -14469,13 +14968,17 @@
       </c>
       <c r="D154" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E154" s="28" t="inlineStr"/>
+          <t>trước khi cấy implant cần kiêng gì</t>
+        </is>
+      </c>
+      <c r="E154" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F154" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G154" s="28" t="inlineStr">
@@ -14500,12 +15003,16 @@
       </c>
       <c r="K154" s="28" t="inlineStr"/>
       <c r="L154" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M154" s="10" t="inlineStr"/>
-      <c r="N154" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>trước khi cấy implant cần làm gì</t>
+        </is>
+      </c>
+      <c r="N154" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: ngưng thuốc lá theo chỉ định, báo đầy đủ thuốc đang dùng (nhất là thuốc chống đông và chống huỷ xương), ăn nhẹ trước khi làm, không tự ý ngưng thuốc bệnh nền.</t>
         </is>
       </c>
       <c r="O154" s="10" t="inlineStr">
@@ -14515,7 +15022,7 @@
       </c>
       <c r="P154" s="10" t="inlineStr">
         <is>
-          <t>R13 · R1</t>
+          <t>R13 · Không hướng dẫn tự ngưng thuốc</t>
         </is>
       </c>
       <c r="Q154" s="10" t="inlineStr">
@@ -14542,18 +15049,22 @@
       </c>
       <c r="D155" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E155" s="28" t="inlineStr"/>
+          <t>cấy implant vào mùa nào tốt nhất</t>
+        </is>
+      </c>
+      <c r="E155" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F155" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="G155" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H155" s="28" t="inlineStr">
@@ -14573,12 +15084,16 @@
       </c>
       <c r="K155" s="28" t="inlineStr"/>
       <c r="L155" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M155" s="10" t="inlineStr"/>
-      <c r="N155" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>3</v>
+      </c>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>thời điểm cấy implant</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không có mùa tốt hơn về mặt y khoa. Yếu tố thật sự nên cân nhắc là lịch cá nhân — tránh giai đoạn công tác liên tục khiến bỏ tái khám.</t>
         </is>
       </c>
       <c r="O155" s="10" t="inlineStr">
@@ -14615,13 +15130,17 @@
       </c>
       <c r="D156" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E156" s="28" t="inlineStr"/>
+          <t>có thể cấy implant và nhổ răng trong cùng một buổi không</t>
+        </is>
+      </c>
+      <c r="E156" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F156" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G156" s="28" t="inlineStr">
@@ -14646,12 +15165,16 @@
       </c>
       <c r="K156" s="28" t="inlineStr"/>
       <c r="L156" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M156" s="10" t="inlineStr"/>
-      <c r="N156" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>nhổ răng và cấy cùng buổi</t>
+        </is>
+      </c>
+      <c r="N156" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: được trong ca cấy tức thì có chỉ định phù hợp — xương còn tốt, không nhiễm trùng. Không phải lựa chọn mặc định; sai chỉ định làm tăng nguy cơ thất bại.</t>
         </is>
       </c>
       <c r="O156" s="10" t="inlineStr">
@@ -14688,13 +15211,17 @@
       </c>
       <c r="D157" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E157" s="28" t="inlineStr"/>
+          <t>sau khi gắn mão implant có cần làm gì thêm không</t>
+        </is>
+      </c>
+      <c r="E157" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F157" s="28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="G157" s="28" t="inlineStr">
@@ -14719,12 +15246,16 @@
       </c>
       <c r="K157" s="28" t="inlineStr"/>
       <c r="L157" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="M157" s="10" t="inlineStr"/>
-      <c r="N157" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M157" s="10" t="inlineStr">
+        <is>
+          <t>sau khi gắn mão implant</t>
+        </is>
+      </c>
+      <c r="N157" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: kiểm tra khớp cắn sau 1–2 tuần sử dụng, học cách vệ sinh kẽ quanh trụ bằng chỉ nha khoa chuyên dụng hoặc tăm nước, và chốt lịch tái khám định kỳ.</t>
         </is>
       </c>
       <c r="O157" s="10" t="inlineStr">
@@ -14761,18 +15292,22 @@
       </c>
       <c r="D158" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E158" s="28" t="inlineStr"/>
+          <t>người bị tiểu đường có trồng răng implant được không</t>
+        </is>
+      </c>
+      <c r="E158" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F158" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G158" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H158" s="28" t="inlineStr">
@@ -14792,12 +15327,16 @@
       </c>
       <c r="K158" s="28" t="inlineStr"/>
       <c r="L158" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M158" s="10" t="inlineStr"/>
-      <c r="N158" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M158" s="10" t="inlineStr">
+        <is>
+          <t>implant cho người tiểu đường</t>
+        </is>
+      </c>
+      <c r="N158" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: làm được khi đường huyết kiểm soát ổn định và được bác sĩ nội khoa đồng ý. Đường huyết cao làm chậm lành thương, tăng nhiễm trùng và tăng nguy cơ viêm quanh trụ. Bắt buộc phối hợp nội khoa, không kết luận thay bác sĩ.</t>
         </is>
       </c>
       <c r="O158" s="10" t="inlineStr">
@@ -14807,7 +15346,7 @@
       </c>
       <c r="P158" s="10" t="inlineStr">
         <is>
-          <t>R13 · R8</t>
+          <t>R13 · Mời thăm khám, không chẩn đoán</t>
         </is>
       </c>
       <c r="Q158" s="10" t="inlineStr">
@@ -14834,18 +15373,22 @@
       </c>
       <c r="D159" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E159" s="28" t="inlineStr"/>
+          <t>người cao tuổi 70 tuổi có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E159" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F159" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G159" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H159" s="28" t="inlineStr">
@@ -14865,12 +15408,16 @@
       </c>
       <c r="K159" s="28" t="inlineStr"/>
       <c r="L159" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M159" s="10" t="inlineStr"/>
-      <c r="N159" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M159" s="10" t="inlineStr">
+        <is>
+          <t>implant cho người 70 tuổi</t>
+        </is>
+      </c>
+      <c r="N159" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tuổi không phải chống chỉ định — điều quyết định là sức khoẻ toàn thân, thuốc đang dùng và khả năng theo đuổi tái khám. Nhiều ca người cao tuổi làm tốt. Cần đánh giá nội khoa trước.</t>
         </is>
       </c>
       <c r="O159" s="10" t="inlineStr">
@@ -14907,18 +15454,22 @@
       </c>
       <c r="D160" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E160" s="28" t="inlineStr"/>
+          <t>Mẹ em đang uống thuốc chống loãng xương dạng tiêm. Bác sĩ nói không cấy implant được, có đúng không ạ?</t>
+        </is>
+      </c>
+      <c r="E160" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F160" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G160" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H160" s="28" t="inlineStr">
@@ -14938,12 +15489,16 @@
       </c>
       <c r="K160" s="28" t="inlineStr"/>
       <c r="L160" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M160" s="10" t="inlineStr"/>
-      <c r="N160" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M160" s="10" t="inlineStr">
+        <is>
+          <t>thuốc chống loãng xương và implant</t>
+        </is>
+      </c>
+      <c r="N160" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thuốc chống huỷ xương, nhất là đường tiêm liều cao, liên quan tới nguy cơ hoại tử xương hàm — nên đây là cảnh báo có cơ sở. Hướng xử lý phải do bác sĩ răng hàm mặt phối hợp bác sĩ kê đơn quyết định, không tự ngưng thuốc.</t>
         </is>
       </c>
       <c r="O160" s="10" t="inlineStr">
@@ -14953,7 +15508,7 @@
       </c>
       <c r="P160" s="10" t="inlineStr">
         <is>
-          <t>R13 · R8</t>
+          <t>R13 · Không phủ nhận ý kiến bác sĩ, không hướng dẫn ngưng thuốc</t>
         </is>
       </c>
       <c r="Q160" s="10" t="inlineStr">
@@ -14980,18 +15535,22 @@
       </c>
       <c r="D161" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E161" s="28" t="inlineStr"/>
+          <t>người bị cao huyết áp có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E161" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F161" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G161" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H161" s="28" t="inlineStr">
@@ -15011,12 +15570,16 @@
       </c>
       <c r="K161" s="28" t="inlineStr"/>
       <c r="L161" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M161" s="10" t="inlineStr"/>
-      <c r="N161" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>cao huyết áp và implant</t>
+        </is>
+      </c>
+      <c r="N161" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: làm được khi huyết áp được kiểm soát; cần đo huyết áp trước thủ thuật và thông báo thuốc đang dùng. Một số thuốc ảnh hưởng chảy máu nên phải khai báo đầy đủ.</t>
         </is>
       </c>
       <c r="O161" s="10" t="inlineStr">
@@ -15053,18 +15616,22 @@
       </c>
       <c r="D162" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E162" s="28" t="inlineStr"/>
+          <t>đang mang thai có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E162" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F162" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G162" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H162" s="28" t="inlineStr">
@@ -15084,12 +15651,16 @@
       </c>
       <c r="K162" s="28" t="inlineStr"/>
       <c r="L162" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M162" s="10" t="inlineStr"/>
-      <c r="N162" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M162" s="10" t="inlineStr">
+        <is>
+          <t>mang thai và implant</t>
+        </is>
+      </c>
+      <c r="N162" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường hoãn tới sau sinh vì liên quan chụp phim, thuốc và tư thế nằm lâu. Cấp cứu nha khoa vẫn xử lý được với biện pháp bảo vệ phù hợp. Quyết định do bác sĩ sản và bác sĩ RHM phối hợp.</t>
         </is>
       </c>
       <c r="O162" s="10" t="inlineStr">
@@ -15126,18 +15697,22 @@
       </c>
       <c r="D163" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E163" s="28" t="inlineStr"/>
+          <t>người bị tim mạch đang uống thuốc chống đông có cấy được không</t>
+        </is>
+      </c>
+      <c r="E163" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F163" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G163" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H163" s="28" t="inlineStr">
@@ -15157,12 +15732,16 @@
       </c>
       <c r="K163" s="28" t="inlineStr"/>
       <c r="L163" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M163" s="10" t="inlineStr"/>
-      <c r="N163" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>thuốc chống đông và implant</t>
+        </is>
+      </c>
+      <c r="N163" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cần đánh giá nguy cơ chảy máu và phối hợp với bác sĩ tim mạch; TUYỆT ĐỐI không tự ngưng thuốc chống đông để đi làm răng. Nhiều ca làm được mà không cần ngưng thuốc.</t>
         </is>
       </c>
       <c r="O163" s="10" t="inlineStr">
@@ -15172,7 +15751,7 @@
       </c>
       <c r="P163" s="10" t="inlineStr">
         <is>
-          <t>R13 · R8</t>
+          <t>R13 · Không hướng dẫn tự ngưng thuốc</t>
         </is>
       </c>
       <c r="Q163" s="10" t="inlineStr">
@@ -15199,18 +15778,22 @@
       </c>
       <c r="D164" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E164" s="28" t="inlineStr"/>
+          <t>người hút thuốc lá nhiều có nên cấy implant không</t>
+        </is>
+      </c>
+      <c r="E164" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F164" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G164" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H164" s="28" t="inlineStr">
@@ -15230,12 +15813,16 @@
       </c>
       <c r="K164" s="28" t="inlineStr"/>
       <c r="L164" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M164" s="10" t="inlineStr"/>
-      <c r="N164" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M164" s="10" t="inlineStr">
+        <is>
+          <t>hút thuốc và implant</t>
+        </is>
+      </c>
+      <c r="N164" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: làm được nhưng tỷ lệ thất bại cao hơn rõ rệt. Khuyến nghị ngưng thuốc trước và sau cấy theo chỉ định. Nói thẳng điều này ngay từ tư vấn để khách không bất ngờ khi có biến chứng.</t>
         </is>
       </c>
       <c r="O164" s="10" t="inlineStr">
@@ -15272,18 +15859,22 @@
       </c>
       <c r="D165" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E165" s="28" t="inlineStr"/>
+          <t>người bị nghiến răng ban đêm có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E165" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F165" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G165" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H165" s="28" t="inlineStr">
@@ -15303,12 +15894,16 @@
       </c>
       <c r="K165" s="28" t="inlineStr"/>
       <c r="L165" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M165" s="10" t="inlineStr"/>
-      <c r="N165" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M165" s="10" t="inlineStr">
+        <is>
+          <t>nghiến răng và implant</t>
+        </is>
+      </c>
+      <c r="N165" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: làm được nhưng cần máng nhai sau phục hình và cân nhắc số trụ, đường kính trụ để chịu lực. Không điều trị nghiến răng thì nguy cơ gãy vít và vỡ mão cao.</t>
         </is>
       </c>
       <c r="O165" s="10" t="inlineStr">
@@ -15345,18 +15940,22 @@
       </c>
       <c r="D166" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E166" s="28" t="inlineStr"/>
+          <t>Em bị viêm gan B, đi làm răng có phải báo không và có ảnh hưởng gì không ạ?</t>
+        </is>
+      </c>
+      <c r="E166" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F166" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G166" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H166" s="28" t="inlineStr">
@@ -15376,12 +15975,16 @@
       </c>
       <c r="K166" s="28" t="inlineStr"/>
       <c r="L166" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M166" s="10" t="inlineStr"/>
-      <c r="N166" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>viêm gan B và làm răng</t>
+        </is>
+      </c>
+      <c r="N166" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phải khai báo — không phải vì bị từ chối mà vì liên quan đánh giá đông máu và quy trình vô khuẩn. Cơ sở tuân thủ vô khuẩn chuẩn thì xử lý được. Khai báo bệnh nền là quyền lợi của chính khách.</t>
         </is>
       </c>
       <c r="O166" s="10" t="inlineStr">
@@ -15418,18 +16021,22 @@
       </c>
       <c r="D167" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E167" s="28" t="inlineStr"/>
+          <t>người đang xạ trị vùng đầu cổ có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E167" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F167" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G167" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H167" s="28" t="inlineStr">
@@ -15449,12 +16056,16 @@
       </c>
       <c r="K167" s="28" t="inlineStr"/>
       <c r="L167" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M167" s="10" t="inlineStr"/>
-      <c r="N167" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>xạ trị và implant</t>
+        </is>
+      </c>
+      <c r="N167" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: xạ trị vùng hàm mặt làm tăng nguy cơ hoại tử xương, là tình huống phải rất thận trọng và thường hoãn. Quyết định do hội chẩn giữa bác sĩ ung bướu và bác sĩ RHM.</t>
         </is>
       </c>
       <c r="O167" s="10" t="inlineStr">
@@ -15491,13 +16102,17 @@
       </c>
       <c r="D168" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E168" s="28" t="inlineStr"/>
+          <t>trẻ em mất răng vĩnh viễn có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E168" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F168" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G168" s="28" t="inlineStr">
@@ -15522,12 +16137,16 @@
       </c>
       <c r="K168" s="28" t="inlineStr"/>
       <c r="L168" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M168" s="10" t="inlineStr"/>
-      <c r="N168" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M168" s="10" t="inlineStr">
+        <is>
+          <t>implant cho trẻ em</t>
+        </is>
+      </c>
+      <c r="N168" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không cấy khi xương hàm chưa phát triển xong — thường chờ sau 18–20 tuổi, đánh giá bằng phim. Trong thời gian chờ có phương án giữ khoảng và phục hình tạm. Dẫn sang bộ Nha khoa trẻ em.</t>
         </is>
       </c>
       <c r="O168" s="10" t="inlineStr">
@@ -15564,18 +16183,22 @@
       </c>
       <c r="D169" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E169" s="28" t="inlineStr"/>
+          <t>người bị loãng xương uống thuốc dạng viên có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E169" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F169" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G169" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H169" s="28" t="inlineStr">
@@ -15595,12 +16218,16 @@
       </c>
       <c r="K169" s="28" t="inlineStr"/>
       <c r="L169" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M169" s="10" t="inlineStr"/>
-      <c r="N169" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>18</v>
+      </c>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>thuốc loãng xương dạng viên implant</t>
+        </is>
+      </c>
+      <c r="N169" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nguy cơ thấp hơn đường tiêm nhưng vẫn phải khai báo thời gian dùng thuốc. Bác sĩ sẽ cân nhắc dựa trên loại thuốc, liều và thời gian sử dụng.</t>
         </is>
       </c>
       <c r="O169" s="10" t="inlineStr">
@@ -15637,18 +16264,22 @@
       </c>
       <c r="D170" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E170" s="28" t="inlineStr"/>
+          <t>người bị viêm nha chu nặng có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E170" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F170" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G170" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H170" s="28" t="inlineStr">
@@ -15668,12 +16299,16 @@
       </c>
       <c r="K170" s="28" t="inlineStr"/>
       <c r="L170" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M170" s="10" t="inlineStr"/>
-      <c r="N170" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>viêm nha chu nặng và implant</t>
+        </is>
+      </c>
+      <c r="N170" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phải điều trị ổn định nha chu trước. Người có tiền sử nha chu nặng vẫn cấy được nhưng thuộc nhóm nguy cơ viêm quanh trụ cao, cần lịch tái khám dày hơn. Nói rõ ngay từ đầu.</t>
         </is>
       </c>
       <c r="O170" s="10" t="inlineStr">
@@ -15710,18 +16345,22 @@
       </c>
       <c r="D171" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E171" s="28" t="inlineStr"/>
+          <t>người gầy yếu thiếu canxi có ảnh hưởng tới implant không</t>
+        </is>
+      </c>
+      <c r="E171" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F171" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G171" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H171" s="28" t="inlineStr">
@@ -15743,10 +16382,14 @@
       <c r="L171" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="M171" s="10" t="inlineStr"/>
-      <c r="N171" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>thiếu canxi và implant</t>
+        </is>
+      </c>
+      <c r="N171" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thể trạng chung ảnh hưởng gián tiếp tới lành thương, nhưng yếu tố quyết định là mật độ xương TẠI VÙNG CẤY đo trên CT, không phải cân nặng. Tránh suy diễn từ thể trạng.</t>
         </is>
       </c>
       <c r="O171" s="10" t="inlineStr">
@@ -15783,18 +16426,22 @@
       </c>
       <c r="D172" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E172" s="28" t="inlineStr"/>
+          <t>Việt kiều về nước ngắn ngày có làm implant kịp không</t>
+        </is>
+      </c>
+      <c r="E172" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F172" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G172" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H172" s="28" t="inlineStr">
@@ -15814,12 +16461,16 @@
       </c>
       <c r="K172" s="28" t="inlineStr"/>
       <c r="L172" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M172" s="10" t="inlineStr"/>
-      <c r="N172" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M172" s="10" t="inlineStr">
+        <is>
+          <t>Việt kiều làm implant</t>
+        </is>
+      </c>
+      <c r="N172" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường không hoàn tất trong một chuyến ngắn vì phải chờ tích hợp. Phương án thực tế: cấy trụ chuyến này, phục hình chuyến sau; hoặc phối hợp theo dõi từ xa. Nêu rõ điều kiện tiếp nhận.</t>
         </is>
       </c>
       <c r="O172" s="10" t="inlineStr">
@@ -15829,12 +16480,12 @@
       </c>
       <c r="P172" s="10" t="inlineStr">
         <is>
-          <t>R13 · R8</t>
+          <t>R8 · Điều kiện tiếp nhận khách nước ngoài</t>
         </is>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
-          <t>Bệnh lý nền &amp; người cao tuổi</t>
+          <t>Khách tỉnh &amp; Việt kiều</t>
         </is>
       </c>
     </row>
@@ -15856,13 +16507,17 @@
       </c>
       <c r="D173" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E173" s="28" t="inlineStr"/>
+          <t>người đang dùng thuốc ức chế miễn dịch có cấy implant được không</t>
+        </is>
+      </c>
+      <c r="E173" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F173" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G173" s="28" t="inlineStr">
@@ -15887,12 +16542,16 @@
       </c>
       <c r="K173" s="28" t="inlineStr"/>
       <c r="L173" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M173" s="10" t="inlineStr"/>
-      <c r="N173" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>thuốc ức chế miễn dịch implant</t>
+        </is>
+      </c>
+      <c r="N173" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cần phối hợp với bác sĩ điều trị để đánh giá nguy cơ nhiễm trùng và lành thương. Không tự ngưng thuốc. Có ca vẫn thực hiện được với dự phòng phù hợp.</t>
         </is>
       </c>
       <c r="O173" s="10" t="inlineStr">
@@ -15902,7 +16561,7 @@
       </c>
       <c r="P173" s="10" t="inlineStr">
         <is>
-          <t>R13 · R8</t>
+          <t>R13 · Không hướng dẫn tự ngưng thuốc</t>
         </is>
       </c>
       <c r="Q173" s="10" t="inlineStr">
@@ -15929,13 +16588,17 @@
       </c>
       <c r="D174" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E174" s="28" t="inlineStr"/>
+          <t>người sợ nha sĩ, sợ tiếng khoan thì làm implant kiểu gì</t>
+        </is>
+      </c>
+      <c r="E174" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F174" s="28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G174" s="28" t="inlineStr">
@@ -15960,12 +16623,16 @@
       </c>
       <c r="K174" s="28" t="inlineStr"/>
       <c r="L174" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M174" s="10" t="inlineStr"/>
-      <c r="N174" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>12</v>
+      </c>
+      <c r="M174" s="10" t="inlineStr">
+        <is>
+          <t>sợ nha sĩ làm implant</t>
+        </is>
+      </c>
+      <c r="N174" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có phương án giảm lo âu — buổi làm quen không can thiệp, hẹn giờ vắng, gây tê đủ sâu, và cân nhắc an thần có theo dõi ở ca nặng. Nói rõ khách có quyền dừng giữa chừng để nghỉ.</t>
         </is>
       </c>
       <c r="O174" s="10" t="inlineStr">
@@ -16002,10 +16669,14 @@
       </c>
       <c r="D175" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E175" s="28" t="inlineStr"/>
+          <t>chăm sóc răng implant như thế nào cho đúng</t>
+        </is>
+      </c>
+      <c r="E175" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F175" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16035,10 +16706,14 @@
       <c r="L175" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M175" s="10" t="inlineStr"/>
-      <c r="N175" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M175" s="10" t="inlineStr">
+        <is>
+          <t>chăm sóc răng implant</t>
+        </is>
+      </c>
+      <c r="N175" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 3 việc mỗi ngày — chải đủ 2 lần với bàn chải lông mềm, làm sạch KẼ quanh trụ bằng chỉ chuyên dụng hoặc tăm nước, và kiểm tra lợi quanh trụ xem có chảy máu không. Trụ không sâu răng được nhưng lợi quanh trụ vẫn viêm được.</t>
         </is>
       </c>
       <c r="O175" s="10" t="inlineStr">
@@ -16075,10 +16750,14 @@
       </c>
       <c r="D176" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E176" s="28" t="inlineStr"/>
+          <t>có nên dùng tăm nước cho răng implant không</t>
+        </is>
+      </c>
+      <c r="E176" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F176" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16108,10 +16787,14 @@
       <c r="L176" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M176" s="10" t="inlineStr"/>
-      <c r="N176" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M176" s="10" t="inlineStr">
+        <is>
+          <t>tăm nước cho implant</t>
+        </is>
+      </c>
+      <c r="N176" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nên — tăm nước làm sạch vùng kẽ quanh trụ hiệu quả hơn chỉ nha khoa thông thường với nhiều người. Dùng áp lực vừa, hướng vuông góc với viền lợi.</t>
         </is>
       </c>
       <c r="O176" s="10" t="inlineStr">
@@ -16148,10 +16831,14 @@
       </c>
       <c r="D177" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E177" s="28" t="inlineStr"/>
+          <t>bao lâu tái khám implant một lần</t>
+        </is>
+      </c>
+      <c r="E177" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F177" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16181,10 +16868,14 @@
       <c r="L177" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M177" s="10" t="inlineStr"/>
-      <c r="N177" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M177" s="10" t="inlineStr">
+        <is>
+          <t>tái khám implant định kỳ</t>
+        </is>
+      </c>
+      <c r="N177" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: năm đầu khám dày theo lịch bác sĩ, sau đó 6–12 tháng một lần gồm kiểm tra khớp cắn, làm sạch quanh trụ và chụp phim theo dõi xương. Bỏ tái khám thường là điều kiện loại trừ bảo hành.</t>
         </is>
       </c>
       <c r="O177" s="10" t="inlineStr">
@@ -16221,10 +16912,14 @@
       </c>
       <c r="D178" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E178" s="28" t="inlineStr"/>
+          <t>răng implant có bị sâu không</t>
+        </is>
+      </c>
+      <c r="E178" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F178" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16232,7 +16927,7 @@
       </c>
       <c r="G178" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H178" s="28" t="inlineStr">
@@ -16252,12 +16947,16 @@
       </c>
       <c r="K178" s="28" t="inlineStr"/>
       <c r="L178" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M178" s="10" t="inlineStr"/>
-      <c r="N178" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M178" s="10" t="inlineStr">
+        <is>
+          <t>implant có bị sâu không</t>
+        </is>
+      </c>
+      <c r="N178" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: trụ và mão không sâu được vì không phải mô răng — nhưng LỢI và XƯƠNG quanh trụ vẫn viêm và tiêu được. Đây là hiểu nhầm phổ biến khiến khách lơ là vệ sinh.</t>
         </is>
       </c>
       <c r="O178" s="10" t="inlineStr">
@@ -16294,18 +16993,22 @@
       </c>
       <c r="D179" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E179" s="28" t="inlineStr"/>
+          <t>sau cấy implant bị chảy máu kéo dài phải làm sao</t>
+        </is>
+      </c>
+      <c r="E179" s="28" t="inlineStr">
+        <is>
+          <t>Cấp cứu</t>
+        </is>
+      </c>
       <c r="F179" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G179" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H179" s="28" t="inlineStr">
@@ -16325,12 +17028,16 @@
       </c>
       <c r="K179" s="28" t="inlineStr"/>
       <c r="L179" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M179" s="10" t="inlineStr"/>
-      <c r="N179" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M179" s="10" t="inlineStr">
+        <is>
+          <t>chảy máu sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N179" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cắn gạc chặt 30–45 phút, ngồi thẳng, không súc miệng mạnh, không khạc nhổ. Chảy máu không cầm sau 1 giờ hoặc chảy thành dòng thì quay lại cơ sở ngay. Không tự dùng thuốc cầm máu.</t>
         </is>
       </c>
       <c r="O179" s="10" t="inlineStr">
@@ -16340,7 +17047,7 @@
       </c>
       <c r="P179" s="10" t="inlineStr">
         <is>
-          <t>R0 · R13</t>
+          <t>R13 · Hướng về cơ sở y tế, không kê đơn</t>
         </is>
       </c>
       <c r="Q179" s="10" t="inlineStr">
@@ -16367,18 +17074,22 @@
       </c>
       <c r="D180" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E180" s="28" t="inlineStr"/>
+          <t>dấu hiệu nào sau cấy implant là phải quay lại ngay</t>
+        </is>
+      </c>
+      <c r="E180" s="28" t="inlineStr">
+        <is>
+          <t>Cấp cứu</t>
+        </is>
+      </c>
       <c r="F180" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="G180" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H180" s="28" t="inlineStr">
@@ -16398,12 +17109,16 @@
       </c>
       <c r="K180" s="28" t="inlineStr"/>
       <c r="L180" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M180" s="10" t="inlineStr"/>
-      <c r="N180" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>27</v>
+      </c>
+      <c r="M180" s="10" t="inlineStr">
+        <is>
+          <t>dấu hiệu bất thường sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N180" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khối DẤU HIỆU PHẢI QUAY LẠI NGAY — đau tự phát về đêm không đỡ bằng thuốc, sưng tăng lại sau ngày thứ 4, sốt, chảy mủ, tê môi cằm kéo dài, trụ lung lay. Đặt khối này ở đầu mọi bài hậu điều trị.</t>
         </is>
       </c>
       <c r="O180" s="10" t="inlineStr">
@@ -16440,10 +17155,14 @@
       </c>
       <c r="D181" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E181" s="28" t="inlineStr"/>
+          <t>vệ sinh răng implant khác răng thật chỗ nào</t>
+        </is>
+      </c>
+      <c r="E181" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F181" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16473,10 +17192,14 @@
       <c r="L181" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M181" s="10" t="inlineStr"/>
-      <c r="N181" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M181" s="10" t="inlineStr">
+        <is>
+          <t>vệ sinh implant khác răng thật</t>
+        </is>
+      </c>
+      <c r="N181" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khác ở vùng cổ trụ — không có dây chằng nha chu nên hàng rào bảo vệ yếu hơn, vi khuẩn dễ đi sâu hơn. Vì vậy làm sạch kẽ quan trọng hơn hẳn so với răng thật.</t>
         </is>
       </c>
       <c r="O181" s="10" t="inlineStr">
@@ -16513,13 +17236,17 @@
       </c>
       <c r="D182" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E182" s="28" t="inlineStr"/>
+          <t>bị hôi miệng quanh răng implant phải làm sao</t>
+        </is>
+      </c>
+      <c r="E182" s="28" t="inlineStr">
+        <is>
+          <t>Xử lý</t>
+        </is>
+      </c>
       <c r="F182" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G182" s="28" t="inlineStr">
@@ -16546,10 +17273,14 @@
       <c r="L182" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M182" s="10" t="inlineStr"/>
-      <c r="N182" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M182" s="10" t="inlineStr">
+        <is>
+          <t>hôi miệng quanh implant</t>
+        </is>
+      </c>
+      <c r="N182" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường do khe hở giữa mão và trụ hoặc viêm quanh trụ — không giải quyết được bằng nước súc miệng. Cần khám để xác định nguyên nhân cơ học hay viêm.</t>
         </is>
       </c>
       <c r="O182" s="10" t="inlineStr">
@@ -16586,10 +17317,14 @@
       </c>
       <c r="D183" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E183" s="28" t="inlineStr"/>
+          <t>có cần lấy cao răng cho implant không</t>
+        </is>
+      </c>
+      <c r="E183" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F183" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16619,10 +17354,14 @@
       <c r="L183" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M183" s="10" t="inlineStr"/>
-      <c r="N183" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M183" s="10" t="inlineStr">
+        <is>
+          <t>lấy cao răng cho implant</t>
+        </is>
+      </c>
+      <c r="N183" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có, nhưng phải dùng dụng cụ chuyên dụng không làm xước bề mặt trụ. Báo rõ với kỹ thuật viên là có implant trước khi làm sạch.</t>
         </is>
       </c>
       <c r="O183" s="10" t="inlineStr">
@@ -16659,10 +17398,14 @@
       </c>
       <c r="D184" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E184" s="28" t="inlineStr"/>
+          <t>sau cấy implant có được tập thể thao không</t>
+        </is>
+      </c>
+      <c r="E184" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F184" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16670,7 +17413,7 @@
       </c>
       <c r="G184" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H184" s="28" t="inlineStr">
@@ -16690,12 +17433,16 @@
       </c>
       <c r="K184" s="28" t="inlineStr"/>
       <c r="L184" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M184" s="10" t="inlineStr"/>
-      <c r="N184" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M184" s="10" t="inlineStr">
+        <is>
+          <t>tập thể thao sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N184" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nghỉ vận động mạnh 3–7 ngày đầu để tránh tăng áp lực gây chảy máu và sưng. Đi bộ nhẹ thì bình thường.</t>
         </is>
       </c>
       <c r="O184" s="10" t="inlineStr">
@@ -16732,13 +17479,17 @@
       </c>
       <c r="D185" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E185" s="28" t="inlineStr"/>
+          <t>răng implant bị cộm khi nhai phải làm sao</t>
+        </is>
+      </c>
+      <c r="E185" s="28" t="inlineStr">
+        <is>
+          <t>Xử lý</t>
+        </is>
+      </c>
       <c r="F185" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G185" s="28" t="inlineStr">
@@ -16765,10 +17516,14 @@
       <c r="L185" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M185" s="10" t="inlineStr"/>
-      <c r="N185" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M185" s="10" t="inlineStr">
+        <is>
+          <t>implant bị cộm</t>
+        </is>
+      </c>
+      <c r="N185" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là dấu hiệu khớp cắn cần chỉnh — nên quay lại trong vài ngày. Để lâu gây quá tải, dẫn tới gãy vít hoặc tiêu xương quanh trụ.</t>
         </is>
       </c>
       <c r="O185" s="10" t="inlineStr">
@@ -16805,10 +17560,14 @@
       </c>
       <c r="D186" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E186" s="28" t="inlineStr"/>
+          <t>có được dùng nước súc miệng sau cấy implant không</t>
+        </is>
+      </c>
+      <c r="E186" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F186" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16816,7 +17575,7 @@
       </c>
       <c r="G186" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H186" s="28" t="inlineStr">
@@ -16836,12 +17595,16 @@
       </c>
       <c r="K186" s="28" t="inlineStr"/>
       <c r="L186" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M186" s="10" t="inlineStr"/>
-      <c r="N186" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M186" s="10" t="inlineStr">
+        <is>
+          <t>nước súc miệng sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N186" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dùng theo chỉ định của bác sĩ về loại và thời gian; không súc mạnh trong 24 giờ đầu. Không tự mua loại chứa cồn mạnh cho vùng mới phẫu thuật.</t>
         </is>
       </c>
       <c r="O186" s="10" t="inlineStr">
@@ -16878,10 +17641,14 @@
       </c>
       <c r="D187" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E187" s="28" t="inlineStr"/>
+          <t>implant dùng được bao nhiêu năm</t>
+        </is>
+      </c>
+      <c r="E187" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F187" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16911,10 +17678,14 @@
       <c r="L187" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M187" s="10" t="inlineStr"/>
-      <c r="N187" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M187" s="10" t="inlineStr">
+        <is>
+          <t>implant dùng được bao lâu</t>
+        </is>
+      </c>
+      <c r="N187" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tuổi thọ phụ thuộc vệ sinh, tái khám và kiểm soát bệnh nền — không có con số cố định và KHÔNG dùng chữ vĩnh viễn. Phần mão có thể phải thay trước phần trụ.</t>
         </is>
       </c>
       <c r="O187" s="10" t="inlineStr">
@@ -16924,7 +17695,7 @@
       </c>
       <c r="P187" s="10" t="inlineStr">
         <is>
-          <t>R0 · R13</t>
+          <t>R1 · Cấm “vĩnh viễn / trọn đời”</t>
         </is>
       </c>
       <c r="Q187" s="10" t="inlineStr">
@@ -16951,10 +17722,14 @@
       </c>
       <c r="D188" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E188" s="28" t="inlineStr"/>
+          <t>chụp ảnh X-quang theo dõi implant bao lâu một lần</t>
+        </is>
+      </c>
+      <c r="E188" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F188" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16962,7 +17737,7 @@
       </c>
       <c r="G188" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H188" s="28" t="inlineStr">
@@ -16982,12 +17757,16 @@
       </c>
       <c r="K188" s="28" t="inlineStr"/>
       <c r="L188" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M188" s="10" t="inlineStr"/>
-      <c r="N188" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M188" s="10" t="inlineStr">
+        <is>
+          <t>chụp phim theo dõi implant</t>
+        </is>
+      </c>
+      <c r="N188" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: theo chỉ định bác sĩ, thường kèm lịch tái khám định kỳ để so sánh mức xương quanh trụ theo thời gian. So sánh phim theo năm là cách phát hiện sớm tiêu xương.</t>
         </is>
       </c>
       <c r="O188" s="10" t="inlineStr">
@@ -17024,10 +17803,14 @@
       </c>
       <c r="D189" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E189" s="28" t="inlineStr"/>
+          <t>ăn đồ cứng có làm hỏng răng implant không</t>
+        </is>
+      </c>
+      <c r="E189" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F189" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -17057,10 +17840,14 @@
       <c r="L189" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M189" s="10" t="inlineStr"/>
-      <c r="N189" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M189" s="10" t="inlineStr">
+        <is>
+          <t>ăn đồ cứng với implant</t>
+        </is>
+      </c>
+      <c r="N189" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: mão sứ trên implant có thể vỡ khi cắn vật quá cứng (đá, xương, nắp chai). Trụ chịu lực tốt nhưng mão thì không khác gì răng sứ thường.</t>
         </is>
       </c>
       <c r="O189" s="10" t="inlineStr">
@@ -17097,10 +17884,14 @@
       </c>
       <c r="D190" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E190" s="28" t="inlineStr"/>
+          <t>sau cấy implant có được hút thuốc lại không</t>
+        </is>
+      </c>
+      <c r="E190" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F190" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -17130,10 +17921,14 @@
       <c r="L190" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M190" s="10" t="inlineStr"/>
-      <c r="N190" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M190" s="10" t="inlineStr">
+        <is>
+          <t>hút thuốc sau cấy implant</t>
+        </is>
+      </c>
+      <c r="N190" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nên ngưng ít nhất trong giai đoạn lành thương theo chỉ định, và tốt nhất là ngưng hẳn — hút thuốc là yếu tố nguy cơ hàng đầu của viêm quanh trụ về lâu dài.</t>
         </is>
       </c>
       <c r="O190" s="10" t="inlineStr">
@@ -17170,10 +17965,14 @@
       </c>
       <c r="D191" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E191" s="28" t="inlineStr"/>
+          <t>implant có cần đeo máng ban đêm không</t>
+        </is>
+      </c>
+      <c r="E191" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F191" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -17181,7 +17980,7 @@
       </c>
       <c r="G191" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H191" s="28" t="inlineStr">
@@ -17201,12 +18000,16 @@
       </c>
       <c r="K191" s="28" t="inlineStr"/>
       <c r="L191" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M191" s="10" t="inlineStr"/>
-      <c r="N191" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M191" s="10" t="inlineStr">
+        <is>
+          <t>máng nhai cho implant</t>
+        </is>
+      </c>
+      <c r="N191" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cần với người nghiến răng hoặc siết chặt hàm; không bắt buộc với người bình thường. Bác sĩ đánh giá qua dấu mòn trên răng và khớp cắn.</t>
         </is>
       </c>
       <c r="O191" s="10" t="inlineStr">
@@ -17243,10 +18046,14 @@
       </c>
       <c r="D192" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E192" s="28" t="inlineStr"/>
+          <t>mất răng bao lâu thì bị tiêu xương hàm</t>
+        </is>
+      </c>
+      <c r="E192" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F192" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17276,10 +18083,14 @@
       <c r="L192" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M192" s="10" t="inlineStr"/>
-      <c r="N192" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M192" s="10" t="inlineStr">
+        <is>
+          <t>mất răng tiêu xương</t>
+        </is>
+      </c>
+      <c r="N192" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tiêu xương bắt đầu ngay sau khi mất răng và nhanh nhất trong năm đầu, sau đó chậm dần nhưng không dừng. Đây là lý do mất răng càng lâu càng dễ phải ghép xương. Cần bác sĩ thẩm định số liệu.</t>
         </is>
       </c>
       <c r="O192" s="10" t="inlineStr">
@@ -17289,7 +18100,7 @@
       </c>
       <c r="P192" s="10" t="inlineStr">
         <is>
-          <t>R0 · R4</t>
+          <t>R4 · Nội dung y khoa cần BS thẩm định</t>
         </is>
       </c>
       <c r="Q192" s="10" t="inlineStr">
@@ -17316,10 +18127,14 @@
       </c>
       <c r="D193" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E193" s="28" t="inlineStr"/>
+          <t>tiêu xương hàm có phục hồi được không</t>
+        </is>
+      </c>
+      <c r="E193" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F193" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17349,10 +18164,14 @@
       <c r="L193" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M193" s="10" t="inlineStr"/>
-      <c r="N193" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M193" s="10" t="inlineStr">
+        <is>
+          <t>phục hồi xương hàm</t>
+        </is>
+      </c>
+      <c r="N193" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: xương đã tiêu không tự mọc lại; chỉ bù được bằng ghép xương. Cấy implant sớm giúp duy trì xương nhờ truyền lực nhai xuống xương — đây là khác biệt lớn nhất so với cầu răng và hàm tháo lắp.</t>
         </is>
       </c>
       <c r="O193" s="10" t="inlineStr">
@@ -17389,10 +18208,14 @@
       </c>
       <c r="D194" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E194" s="28" t="inlineStr"/>
+          <t>mất răng có làm mặt bị hóp không</t>
+        </is>
+      </c>
+      <c r="E194" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F194" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17422,10 +18245,14 @@
       <c r="L194" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M194" s="10" t="inlineStr"/>
-      <c r="N194" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M194" s="10" t="inlineStr">
+        <is>
+          <t>mất răng mặt hóp</t>
+        </is>
+      </c>
+      <c r="N194" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: mất nhiều răng lâu năm làm giảm chiều cao tầng mặt dưới và tiêu xương ổ răng, gây hóp má và nếp nhăn quanh miệng. Giải thích cơ chế thay vì dùng ảnh gây sợ.</t>
         </is>
       </c>
       <c r="O194" s="10" t="inlineStr">
@@ -17462,10 +18289,14 @@
       </c>
       <c r="D195" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E195" s="28" t="inlineStr"/>
+          <t>implant có ảnh hưởng đến xương hàm không</t>
+        </is>
+      </c>
+      <c r="E195" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F195" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17495,10 +18326,14 @@
       <c r="L195" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M195" s="10" t="inlineStr"/>
-      <c r="N195" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M195" s="10" t="inlineStr">
+        <is>
+          <t>implant và xương hàm</t>
+        </is>
+      </c>
+      <c r="N195" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: implant truyền lực nhai xuống xương nên giúp hạn chế tiêu xương tại vùng đó — khác với cầu răng và hàm tháo lắp không truyền lực xuống xương ổ.</t>
         </is>
       </c>
       <c r="O195" s="10" t="inlineStr">
@@ -17535,10 +18370,14 @@
       </c>
       <c r="D196" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E196" s="28" t="inlineStr"/>
+          <t>nha chu ảnh hưởng thế nào đến implant</t>
+        </is>
+      </c>
+      <c r="E196" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F196" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17568,10 +18407,14 @@
       <c r="L196" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M196" s="10" t="inlineStr"/>
-      <c r="N196" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M196" s="10" t="inlineStr">
+        <is>
+          <t>nha chu và implant</t>
+        </is>
+      </c>
+      <c r="N196" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: vi khuẩn nha chu ở răng thật còn lại là nguồn lây sang vùng quanh trụ. Người có tiền sử nha chu là nhóm nguy cơ viêm quanh trụ cao nhất, cần kiểm soát trước và sau khi cấy.</t>
         </is>
       </c>
       <c r="O196" s="10" t="inlineStr">
@@ -17608,10 +18451,14 @@
       </c>
       <c r="D197" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E197" s="28" t="inlineStr"/>
+          <t>khớp cắn sai có gây mất răng không</t>
+        </is>
+      </c>
+      <c r="E197" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F197" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17619,7 +18466,7 @@
       </c>
       <c r="G197" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H197" s="28" t="inlineStr">
@@ -17639,12 +18486,16 @@
       </c>
       <c r="K197" s="28" t="inlineStr"/>
       <c r="L197" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M197" s="10" t="inlineStr"/>
-      <c r="N197" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M197" s="10" t="inlineStr">
+        <is>
+          <t>khớp cắn sai mất răng</t>
+        </is>
+      </c>
+      <c r="N197" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khớp cắn sai gây quá tải một số răng, lâu dài dẫn tới mòn, nứt và tiêu xương quanh răng đó. Đây là lý do phục hình phải xét toàn hàm chứ không chỉ chỗ mất răng.</t>
         </is>
       </c>
       <c r="O197" s="10" t="inlineStr">
@@ -17681,10 +18532,14 @@
       </c>
       <c r="D198" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E198" s="28" t="inlineStr"/>
+          <t>tích hợp xương trong implant là gì</t>
+        </is>
+      </c>
+      <c r="E198" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F198" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17714,10 +18569,14 @@
       <c r="L198" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M198" s="10" t="inlineStr"/>
-      <c r="N198" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M198" s="10" t="inlineStr">
+        <is>
+          <t>tích hợp xương</t>
+        </is>
+      </c>
+      <c r="N198" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là quá trình tế bào xương bám trực tiếp lên bề mặt trụ titan, tạo liên kết vững chắc — mất 3–6 tháng. Hiểu đúng khái niệm này giúp khách hiểu vì sao không được nhai sớm trên trụ.</t>
         </is>
       </c>
       <c r="O198" s="10" t="inlineStr">
@@ -17754,10 +18613,14 @@
       </c>
       <c r="D199" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E199" s="28" t="inlineStr"/>
+          <t>vì sao implant không bị lung lay như răng thật</t>
+        </is>
+      </c>
+      <c r="E199" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F199" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17765,7 +18628,7 @@
       </c>
       <c r="G199" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H199" s="28" t="inlineStr">
@@ -17785,12 +18648,16 @@
       </c>
       <c r="K199" s="28" t="inlineStr"/>
       <c r="L199" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M199" s="10" t="inlineStr"/>
-      <c r="N199" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M199" s="10" t="inlineStr">
+        <is>
+          <t>implant và dây chằng nha chu</t>
+        </is>
+      </c>
+      <c r="N199" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: răng thật có dây chằng nha chu cho phép dịch chuyển vi mô và cảm nhận lực; trụ implant bám trực tiếp vào xương nên cứng hơn và KHÔNG có cảm giác lực. Hệ quả: dễ quá tải mà không tự biết.</t>
         </is>
       </c>
       <c r="O199" s="10" t="inlineStr">
@@ -17827,18 +18694,22 @@
       </c>
       <c r="D200" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E200" s="28" t="inlineStr"/>
+          <t>mất răng có ảnh hưởng đến tiêu hoá không</t>
+        </is>
+      </c>
+      <c r="E200" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F200" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="G200" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H200" s="28" t="inlineStr">
@@ -17858,12 +18729,16 @@
       </c>
       <c r="K200" s="28" t="inlineStr"/>
       <c r="L200" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M200" s="10" t="inlineStr"/>
-      <c r="N200" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>3</v>
+      </c>
+      <c r="M200" s="10" t="inlineStr">
+        <is>
+          <t>mất răng và tiêu hoá</t>
+        </is>
+      </c>
+      <c r="N200" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: giảm hiệu quả nhai khiến thức ăn xuống dạ dày ở dạng thô hơn, có thể gây khó chịu tiêu hoá ở người mất nhiều răng. Trình bày thận trọng, cần BS thẩm định.</t>
         </is>
       </c>
       <c r="O200" s="10" t="inlineStr">
@@ -17873,7 +18748,7 @@
       </c>
       <c r="P200" s="10" t="inlineStr">
         <is>
-          <t>R0 · R4</t>
+          <t>R4 · Cần BS thẩm định</t>
         </is>
       </c>
       <c r="Q200" s="10" t="inlineStr">
@@ -17900,10 +18775,14 @@
       </c>
       <c r="D201" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E201" s="28" t="inlineStr"/>
+          <t>răng đối diện bị trồi lên khi mất răng là sao</t>
+        </is>
+      </c>
+      <c r="E201" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F201" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -17933,10 +18812,14 @@
       <c r="L201" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M201" s="10" t="inlineStr"/>
-      <c r="N201" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M201" s="10" t="inlineStr">
+        <is>
+          <t>răng trồi khi mất răng</t>
+        </is>
+      </c>
+      <c r="N201" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: răng không có răng đối diện để chạm sẽ trồi dần ra khỏi ổ. Trồi nhiều thì phải mài chỉnh hoặc nhổ trước khi phục hình — một lý do nữa để không để trống lâu.</t>
         </is>
       </c>
       <c r="O201" s="10" t="inlineStr">
@@ -17973,10 +18856,14 @@
       </c>
       <c r="D202" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E202" s="28" t="inlineStr"/>
+          <t>ống thần kinh răng dưới nằm ở đâu</t>
+        </is>
+      </c>
+      <c r="E202" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F202" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18006,10 +18893,14 @@
       <c r="L202" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M202" s="10" t="inlineStr"/>
-      <c r="N202" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M202" s="10" t="inlineStr">
+        <is>
+          <t>ống thần kinh răng dưới</t>
+        </is>
+      </c>
+      <c r="N202" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là ống chứa dây thần kinh chi phối cảm giác môi và cằm, chạy trong xương hàm dưới. Vị trí thay đổi theo từng người nên phải đo trên CT trước khi cấy vùng răng hàm dưới.</t>
         </is>
       </c>
       <c r="O202" s="10" t="inlineStr">
@@ -18046,10 +18937,14 @@
       </c>
       <c r="D203" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E203" s="28" t="inlineStr"/>
+          <t>xoang hàm trên liên quan gì đến trồng răng</t>
+        </is>
+      </c>
+      <c r="E203" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F203" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18079,10 +18974,14 @@
       <c r="L203" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M203" s="10" t="inlineStr"/>
-      <c r="N203" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M203" s="10" t="inlineStr">
+        <is>
+          <t>xoang hàm trên và implant</t>
+        </is>
+      </c>
+      <c r="N203" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: xoang hàm trên nằm ngay trên chân răng hàm trên; khi mất răng, xoang có xu hướng mở rộng xuống làm giảm chiều cao xương — dẫn tới chỉ định nâng xoang.</t>
         </is>
       </c>
       <c r="O203" s="10" t="inlineStr">
@@ -18119,18 +19018,22 @@
       </c>
       <c r="D204" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E204" s="28" t="inlineStr"/>
+          <t>implant có dẫn điện hay gây khó chịu khi thời tiết đổi không</t>
+        </is>
+      </c>
+      <c r="E204" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F204" s="28" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="G204" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H204" s="28" t="inlineStr">
@@ -18150,12 +19053,16 @@
       </c>
       <c r="K204" s="28" t="inlineStr"/>
       <c r="L204" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M204" s="10" t="inlineStr"/>
-      <c r="N204" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>3</v>
+      </c>
+      <c r="M204" s="10" t="inlineStr">
+        <is>
+          <t>implant và thời tiết</t>
+        </is>
+      </c>
+      <c r="N204" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: titan không dẫn nhiệt đáng kể tới mức gây khó chịu, và không có bằng chứng implant nhạy cảm theo thời tiết. Cảm giác ê thường đến từ răng thật kế bên.</t>
         </is>
       </c>
       <c r="O204" s="10" t="inlineStr">
@@ -18192,10 +19099,14 @@
       </c>
       <c r="D205" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E205" s="28" t="inlineStr"/>
+          <t>cấy implant có ảnh hưởng đến phát âm không</t>
+        </is>
+      </c>
+      <c r="E205" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F205" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18203,7 +19114,7 @@
       </c>
       <c r="G205" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H205" s="28" t="inlineStr">
@@ -18223,12 +19134,16 @@
       </c>
       <c r="K205" s="28" t="inlineStr"/>
       <c r="L205" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M205" s="10" t="inlineStr"/>
-      <c r="N205" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M205" s="10" t="inlineStr">
+        <is>
+          <t>implant và phát âm</t>
+        </is>
+      </c>
+      <c r="N205" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: implant đơn lẻ hầu như không ảnh hưởng; phục hình toàn hàm có thể cần vài tuần làm quen. Khác biệt rõ nhất là khi chuyển từ hàm tháo lắp sang cố định.</t>
         </is>
       </c>
       <c r="O205" s="10" t="inlineStr">
@@ -18265,10 +19180,14 @@
       </c>
       <c r="D206" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E206" s="28" t="inlineStr"/>
+          <t>trụ implant có bị gỉ trong miệng không</t>
+        </is>
+      </c>
+      <c r="E206" s="28" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
       <c r="F206" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18276,7 +19195,7 @@
       </c>
       <c r="G206" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H206" s="28" t="inlineStr">
@@ -18296,12 +19215,16 @@
       </c>
       <c r="K206" s="28" t="inlineStr"/>
       <c r="L206" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M206" s="10" t="inlineStr"/>
-      <c r="N206" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M206" s="10" t="inlineStr">
+        <is>
+          <t>trụ implant có gỉ không</t>
+        </is>
+      </c>
+      <c r="N206" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: titan tạo lớp oxit bảo vệ nên không gỉ theo nghĩa thông thường. Vấn đề thực tế không phải ăn mòn mà là tích tụ mảng bám gây viêm quanh trụ.</t>
         </is>
       </c>
       <c r="O206" s="10" t="inlineStr">
@@ -18338,10 +19261,14 @@
       </c>
       <c r="D207" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E207" s="28" t="inlineStr"/>
+          <t>cơ thể có đào thải titan không</t>
+        </is>
+      </c>
+      <c r="E207" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F207" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18371,10 +19298,14 @@
       <c r="L207" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M207" s="10" t="inlineStr"/>
-      <c r="N207" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M207" s="10" t="inlineStr">
+        <is>
+          <t>cơ thể đào thải titan</t>
+        </is>
+      </c>
+      <c r="N207" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: “đào thải” trong implant hầu hết không phải phản ứng miễn dịch với titan mà là mất tích hợp do nhiễm khuẩn hoặc quá tải. Dị ứng titan thật sự rất hiếm.</t>
         </is>
       </c>
       <c r="O207" s="10" t="inlineStr">
@@ -18411,10 +19342,14 @@
       </c>
       <c r="D208" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E208" s="28" t="inlineStr"/>
+          <t>tuổi tác ảnh hưởng thế nào đến lành thương sau cấy implant</t>
+        </is>
+      </c>
+      <c r="E208" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F208" s="28" t="inlineStr">
         <is>
           <t>Warm</t>
@@ -18422,7 +19357,7 @@
       </c>
       <c r="G208" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H208" s="28" t="inlineStr">
@@ -18442,12 +19377,16 @@
       </c>
       <c r="K208" s="28" t="inlineStr"/>
       <c r="L208" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M208" s="10" t="inlineStr"/>
-      <c r="N208" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M208" s="10" t="inlineStr">
+        <is>
+          <t>tuổi tác và lành thương implant</t>
+        </is>
+      </c>
+      <c r="N208" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tuổi làm chậm lành thương ở mức độ nhất định nhưng không phải yếu tố quyết định; bệnh nền và thuốc đang dùng ảnh hưởng nhiều hơn tuổi.</t>
         </is>
       </c>
       <c r="O208" s="10" t="inlineStr">
@@ -18484,10 +19423,14 @@
       </c>
       <c r="D209" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E209" s="28" t="inlineStr"/>
+          <t>trồng được một răng rồi có nên làm nốt các răng còn lại không</t>
+        </is>
+      </c>
+      <c r="E209" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F209" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18517,10 +19460,14 @@
       <c r="L209" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M209" s="10" t="inlineStr"/>
-      <c r="N209" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M209" s="10" t="inlineStr">
+        <is>
+          <t>làm tiếp các răng còn lại</t>
+        </is>
+      </c>
+      <c r="N209" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: xét theo kế hoạch toàn hàm chứ không làm lẻ tẻ — ưu tiên vùng ăn nhai chính, giữ răng thật còn cứu được, và cân nhắc thứ tự để không phải làm lại. Gợi MỘT bước tiếp theo, không bán chồng.</t>
         </is>
       </c>
       <c r="O209" s="10" t="inlineStr">
@@ -18557,13 +19504,17 @@
       </c>
       <c r="D210" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E210" s="28" t="inlineStr"/>
+          <t>mất nhiều răng nên cấy từng trụ hay làm All-On</t>
+        </is>
+      </c>
+      <c r="E210" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F210" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G210" s="28" t="inlineStr">
@@ -18590,10 +19541,14 @@
       <c r="L210" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M210" s="10" t="inlineStr"/>
-      <c r="N210" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M210" s="10" t="inlineStr">
+        <is>
+          <t>cấy từng trụ hay All-On</t>
+        </is>
+      </c>
+      <c r="N210" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: so sánh theo số răng mất, lượng xương còn lại và ngân sách. Dẫn sang bộ All-On 4/6 để xem chi tiết. Nêu rõ All-On không phải lúc nào cũng rẻ hơn.</t>
         </is>
       </c>
       <c r="O210" s="10" t="inlineStr">
@@ -18630,10 +19585,14 @@
       </c>
       <c r="D211" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E211" s="28" t="inlineStr"/>
+          <t>làm implant xong có nên tẩy trắng các răng còn lại không</t>
+        </is>
+      </c>
+      <c r="E211" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F211" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18641,7 +19600,7 @@
       </c>
       <c r="G211" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H211" s="28" t="inlineStr">
@@ -18661,12 +19620,16 @@
       </c>
       <c r="K211" s="28" t="inlineStr"/>
       <c r="L211" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M211" s="10" t="inlineStr"/>
-      <c r="N211" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M211" s="10" t="inlineStr">
+        <is>
+          <t>tẩy trắng sau khi làm implant</t>
+        </is>
+      </c>
+      <c r="N211" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nên tẩy trắng TRƯỚC khi chọn màu mão implant, vì mão sứ không đổi màu theo thuốc tẩy. Làm ngược thứ tự thì mão sẽ lệch màu với răng đã tẩy.</t>
         </is>
       </c>
       <c r="O211" s="10" t="inlineStr">
@@ -18703,10 +19666,14 @@
       </c>
       <c r="D212" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E212" s="28" t="inlineStr"/>
+          <t>sau implant có cần niềng răng không</t>
+        </is>
+      </c>
+      <c r="E212" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F212" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18714,7 +19681,7 @@
       </c>
       <c r="G212" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H212" s="28" t="inlineStr">
@@ -18734,12 +19701,16 @@
       </c>
       <c r="K212" s="28" t="inlineStr"/>
       <c r="L212" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M212" s="10" t="inlineStr"/>
-      <c r="N212" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M212" s="10" t="inlineStr">
+        <is>
+          <t>niềng sau implant</t>
+        </is>
+      </c>
+      <c r="N212" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: trụ implant không di chuyển được bằng khí cụ chỉnh nha — nếu có kế hoạch niềng thì phải tính TRƯỚC khi cấy. Dẫn sang bộ Chỉnh nha.</t>
         </is>
       </c>
       <c r="O212" s="10" t="inlineStr">
@@ -18776,10 +19747,14 @@
       </c>
       <c r="D213" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E213" s="28" t="inlineStr"/>
+          <t>gia đình cùng làm răng có gói nào không</t>
+        </is>
+      </c>
+      <c r="E213" s="28" t="inlineStr">
+        <is>
+          <t>Chi phí</t>
+        </is>
+      </c>
       <c r="F213" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18787,7 +19762,7 @@
       </c>
       <c r="G213" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H213" s="28" t="inlineStr">
@@ -18807,12 +19782,16 @@
       </c>
       <c r="K213" s="28" t="inlineStr"/>
       <c r="L213" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M213" s="10" t="inlineStr"/>
-      <c r="N213" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M213" s="10" t="inlineStr">
+        <is>
+          <t>gói gia đình làm răng</t>
+        </is>
+      </c>
+      <c r="N213" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn về trang gói gia đình và trang ưu đãi hiện hành; không nêu mức giảm trong bài vì là dữ liệu động.</t>
         </is>
       </c>
       <c r="O213" s="10" t="inlineStr">
@@ -18822,7 +19801,7 @@
       </c>
       <c r="P213" s="10" t="inlineStr">
         <is>
-          <t>R0 · R12</t>
+          <t>R12 · Ưu đãi là dữ liệu động</t>
         </is>
       </c>
       <c r="Q213" s="10" t="inlineStr">
@@ -18849,10 +19828,14 @@
       </c>
       <c r="D214" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E214" s="28" t="inlineStr"/>
+          <t>làm implant rồi có cần chăm sóc răng miệng định kỳ cho cả hàm không</t>
+        </is>
+      </c>
+      <c r="E214" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F214" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18882,10 +19865,14 @@
       <c r="L214" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="M214" s="10" t="inlineStr"/>
-      <c r="N214" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M214" s="10" t="inlineStr">
+        <is>
+          <t>chăm sóc định kỳ sau implant</t>
+        </is>
+      </c>
+      <c r="N214" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: có — giữ được trụ phụ thuộc vào sức khoẻ cả hàm, nhất là nha chu của răng thật còn lại. Gợi ý lịch khám tổng quát kèm lấy cao răng.</t>
         </is>
       </c>
       <c r="O214" s="10" t="inlineStr">
@@ -18922,10 +19909,14 @@
       </c>
       <c r="D215" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E215" s="28" t="inlineStr"/>
+          <t>trồng implant xong có làm răng sứ thẩm mỹ được không</t>
+        </is>
+      </c>
+      <c r="E215" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F215" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -18933,7 +19924,7 @@
       </c>
       <c r="G215" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H215" s="28" t="inlineStr">
@@ -18953,12 +19944,16 @@
       </c>
       <c r="K215" s="28" t="inlineStr"/>
       <c r="L215" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M215" s="10" t="inlineStr"/>
-      <c r="N215" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M215" s="10" t="inlineStr">
+        <is>
+          <t>răng sứ sau implant</t>
+        </is>
+      </c>
+      <c r="N215" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: được, nhưng nên lên kế hoạch màu và hình dáng cùng lúc để đồng bộ. Dẫn sang bộ Răng sứ.</t>
         </is>
       </c>
       <c r="O215" s="10" t="inlineStr">
@@ -18995,18 +19990,22 @@
       </c>
       <c r="D216" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E216" s="28" t="inlineStr"/>
+          <t>bố mẹ lớn tuổi mất nhiều răng nên bắt đầu từ đâu</t>
+        </is>
+      </c>
+      <c r="E216" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F216" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="G216" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H216" s="28" t="inlineStr">
@@ -19026,12 +20025,16 @@
       </c>
       <c r="K216" s="28" t="inlineStr"/>
       <c r="L216" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M216" s="10" t="inlineStr"/>
-      <c r="N216" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>3</v>
+      </c>
+      <c r="M216" s="10" t="inlineStr">
+        <is>
+          <t>người già mất nhiều răng bắt đầu từ đâu</t>
+        </is>
+      </c>
+      <c r="N216" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: bắt đầu bằng khám tổng quát và CT để biết xương còn bao nhiêu, rồi mới bàn phương án. Nhấn: đi khám sớm giữ được nhiều lựa chọn hơn.</t>
         </is>
       </c>
       <c r="O216" s="10" t="inlineStr">
@@ -19046,7 +20049,7 @@
       </c>
       <c r="Q216" s="10" t="inlineStr">
         <is>
-          <t>Mất nhiều răng / toàn hàm</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
     </row>
@@ -19068,18 +20071,22 @@
       </c>
       <c r="D217" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E217" s="28" t="inlineStr"/>
+          <t>có nên làm implant cùng lúc với điều trị nha chu không</t>
+        </is>
+      </c>
+      <c r="E217" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F217" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="G217" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H217" s="28" t="inlineStr">
@@ -19099,12 +20106,16 @@
       </c>
       <c r="K217" s="28" t="inlineStr"/>
       <c r="L217" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M217" s="10" t="inlineStr"/>
-      <c r="N217" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M217" s="10" t="inlineStr">
+        <is>
+          <t>implant cùng lúc điều trị nha chu</t>
+        </is>
+      </c>
+      <c r="N217" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: điều trị nha chu trước, ổn định rồi mới cấy. Làm song song làm tăng nguy cơ nhiễm khuẩn vùng cấy.</t>
         </is>
       </c>
       <c r="O217" s="10" t="inlineStr">
@@ -19141,10 +20152,14 @@
       </c>
       <c r="D218" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E218" s="28" t="inlineStr"/>
+          <t>sau implant có cần làm máng chống nghiến không</t>
+        </is>
+      </c>
+      <c r="E218" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F218" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19152,7 +20167,7 @@
       </c>
       <c r="G218" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H218" s="28" t="inlineStr">
@@ -19172,12 +20187,16 @@
       </c>
       <c r="K218" s="28" t="inlineStr"/>
       <c r="L218" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M218" s="10" t="inlineStr"/>
-      <c r="N218" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M218" s="10" t="inlineStr">
+        <is>
+          <t>máng chống nghiến sau implant</t>
+        </is>
+      </c>
+      <c r="N218" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: cần với người nghiến răng — đây là khoản đầu tư nhỏ bảo vệ khoản lớn. Dẫn sang nội dung máng nhai.</t>
         </is>
       </c>
       <c r="O218" s="10" t="inlineStr">
@@ -19214,10 +20233,14 @@
       </c>
       <c r="D219" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E219" s="28" t="inlineStr"/>
+          <t>nên khám răng định kỳ mấy tháng một lần</t>
+        </is>
+      </c>
+      <c r="E219" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F219" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19225,7 +20248,7 @@
       </c>
       <c r="G219" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H219" s="28" t="inlineStr">
@@ -19245,12 +20268,16 @@
       </c>
       <c r="K219" s="28" t="inlineStr"/>
       <c r="L219" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M219" s="10" t="inlineStr"/>
-      <c r="N219" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M219" s="10" t="inlineStr">
+        <is>
+          <t>khám răng định kỳ</t>
+        </is>
+      </c>
+      <c r="N219" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 6 tháng một lần với người bình thường, dày hơn với người có implant hoặc tiền sử nha chu.</t>
         </is>
       </c>
       <c r="O219" s="10" t="inlineStr">
@@ -19287,18 +20314,22 @@
       </c>
       <c r="D220" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E220" s="28" t="inlineStr"/>
+          <t>trẻ con trong nhà nên khám răng từ mấy tuổi</t>
+        </is>
+      </c>
+      <c r="E220" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F220" s="28" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="G220" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H220" s="28" t="inlineStr">
@@ -19318,12 +20349,16 @@
       </c>
       <c r="K220" s="28" t="inlineStr"/>
       <c r="L220" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M220" s="10" t="inlineStr"/>
-      <c r="N220" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>3</v>
+      </c>
+      <c r="M220" s="10" t="inlineStr">
+        <is>
+          <t>trẻ khám răng từ mấy tuổi</t>
+        </is>
+      </c>
+      <c r="N220" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn sang bộ Nha khoa trẻ em — mốc tuổi và nội dung chi tiết nằm ở đó. Chỉ gợi mở một câu, không mở rộng.</t>
         </is>
       </c>
       <c r="O220" s="10" t="inlineStr">
@@ -19360,10 +20395,14 @@
       </c>
       <c r="D221" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E221" s="28" t="inlineStr"/>
+          <t>có chương trình theo dõi implant dài hạn không</t>
+        </is>
+      </c>
+      <c r="E221" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F221" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19371,7 +20410,7 @@
       </c>
       <c r="G221" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H221" s="28" t="inlineStr">
@@ -19391,12 +20430,16 @@
       </c>
       <c r="K221" s="28" t="inlineStr"/>
       <c r="L221" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M221" s="10" t="inlineStr"/>
-      <c r="N221" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M221" s="10" t="inlineStr">
+        <is>
+          <t>theo dõi implant dài hạn</t>
+        </is>
+      </c>
+      <c r="N221" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn về chính sách theo dõi và bảo hành hiện hành; không tự nêu thời hạn hay nội dung gói.</t>
         </is>
       </c>
       <c r="O221" s="10" t="inlineStr">
@@ -19406,7 +20449,7 @@
       </c>
       <c r="P221" s="10" t="inlineStr">
         <is>
-          <t>R0 · R12</t>
+          <t>R12 · Chính sách là dữ liệu động</t>
         </is>
       </c>
       <c r="Q221" s="10" t="inlineStr">
@@ -19433,10 +20476,14 @@
       </c>
       <c r="D222" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E222" s="28" t="inlineStr"/>
+          <t>làm răng ở đâu để cả nhà cùng theo một nơi</t>
+        </is>
+      </c>
+      <c r="E222" s="28" t="inlineStr">
+        <is>
+          <t>Địa phương</t>
+        </is>
+      </c>
       <c r="F222" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19444,7 +20491,7 @@
       </c>
       <c r="G222" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H222" s="28" t="inlineStr">
@@ -19464,12 +20511,16 @@
       </c>
       <c r="K222" s="28" t="inlineStr"/>
       <c r="L222" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M222" s="10" t="inlineStr"/>
-      <c r="N222" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M222" s="10" t="inlineStr">
+        <is>
+          <t>cả nhà làm răng một nơi</t>
+        </is>
+      </c>
+      <c r="N222" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: lợi thế của hệ thống nhiều cơ sở là hồ sơ dùng chung và tái khám được ở nơi gần nhất. Dẫn về trang tìm phòng khám.</t>
         </is>
       </c>
       <c r="O222" s="10" t="inlineStr">
@@ -19479,7 +20530,7 @@
       </c>
       <c r="P222" s="10" t="inlineStr">
         <is>
-          <t>R0 · R12</t>
+          <t>R3 · Đúng cơ sở</t>
         </is>
       </c>
       <c r="Q222" s="10" t="inlineStr">
@@ -19506,10 +20557,14 @@
       </c>
       <c r="D223" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E223" s="28" t="inlineStr"/>
+          <t>sau khi làm implant có cần đổi bàn chải không</t>
+        </is>
+      </c>
+      <c r="E223" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F223" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19517,7 +20572,7 @@
       </c>
       <c r="G223" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H223" s="28" t="inlineStr">
@@ -19537,12 +20592,16 @@
       </c>
       <c r="K223" s="28" t="inlineStr"/>
       <c r="L223" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M223" s="10" t="inlineStr"/>
-      <c r="N223" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M223" s="10" t="inlineStr">
+        <is>
+          <t>bàn chải cho implant</t>
+        </is>
+      </c>
+      <c r="N223" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dùng bàn chải lông mềm và bổ sung dụng cụ làm sạch kẽ; không cần loại đặc biệt đắt tiền.</t>
         </is>
       </c>
       <c r="O223" s="10" t="inlineStr">
@@ -19579,10 +20638,14 @@
       </c>
       <c r="D224" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E224" s="28" t="inlineStr"/>
+          <t>implant có cần kiêng gì lâu dài không</t>
+        </is>
+      </c>
+      <c r="E224" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F224" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19590,7 +20653,7 @@
       </c>
       <c r="G224" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H224" s="28" t="inlineStr">
@@ -19610,12 +20673,16 @@
       </c>
       <c r="K224" s="28" t="inlineStr"/>
       <c r="L224" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M224" s="10" t="inlineStr"/>
-      <c r="N224" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M224" s="10" t="inlineStr">
+        <is>
+          <t>kiêng lâu dài sau implant</t>
+        </is>
+      </c>
+      <c r="N224" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không kiêng gì lâu dài ngoài việc tránh cắn vật quá cứng và duy trì vệ sinh. Thông điệp chính là trấn an.</t>
         </is>
       </c>
       <c r="O224" s="10" t="inlineStr">
@@ -19652,10 +20719,14 @@
       </c>
       <c r="D225" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E225" s="28" t="inlineStr"/>
+          <t>giới thiệu người nhà đi làm răng có ưu đãi không</t>
+        </is>
+      </c>
+      <c r="E225" s="28" t="inlineStr">
+        <is>
+          <t>Chi phí</t>
+        </is>
+      </c>
       <c r="F225" s="28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -19663,7 +20734,7 @@
       </c>
       <c r="G225" s="28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="H225" s="28" t="inlineStr">
@@ -19683,12 +20754,16 @@
       </c>
       <c r="K225" s="28" t="inlineStr"/>
       <c r="L225" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M225" s="10" t="inlineStr"/>
-      <c r="N225" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+        <v>6</v>
+      </c>
+      <c r="M225" s="10" t="inlineStr">
+        <is>
+          <t>giới thiệu người nhà ưu đãi</t>
+        </is>
+      </c>
+      <c r="N225" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn về chương trình hiện hành, không nêu mức. Không lấy giảm giá làm trọng tâm.</t>
         </is>
       </c>
       <c r="O225" s="10" t="inlineStr">
@@ -19698,7 +20773,7 @@
       </c>
       <c r="P225" s="10" t="inlineStr">
         <is>
-          <t>R0 · R12</t>
+          <t>R12 · Ưu đãi là dữ liệu động</t>
         </is>
       </c>
       <c r="Q225" s="10" t="inlineStr">
@@ -19725,10 +20800,14 @@
       </c>
       <c r="D226" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E226" s="28" t="inlineStr"/>
+          <t>mất răng lâu năm có sao không</t>
+        </is>
+      </c>
+      <c r="E226" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F226" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -19758,10 +20837,14 @@
       <c r="L226" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M226" s="10" t="inlineStr"/>
-      <c r="N226" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M226" s="10" t="inlineStr">
+        <is>
+          <t>mất răng lâu năm</t>
+        </is>
+      </c>
+      <c r="N226" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: pillar nền — nêu 4 hệ quả theo thời gian (răng nghiêng, răng trồi, lệch khớp cắn, tiêu xương) và mốc nào thì còn cấy được mà chưa phải ghép xương. Giọng giáo dục, KHÔNG bán.</t>
         </is>
       </c>
       <c r="O226" s="10" t="inlineStr">
@@ -19771,7 +20854,7 @@
       </c>
       <c r="P226" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R0 · Giữ giọng giáo dục, CTA mềm</t>
         </is>
       </c>
       <c r="Q226" s="10" t="inlineStr">
@@ -19798,10 +20881,14 @@
       </c>
       <c r="D227" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E227" s="28" t="inlineStr"/>
+          <t>mất một răng hàm có cần trồng lại không</t>
+        </is>
+      </c>
+      <c r="E227" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F227" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -19831,10 +20918,14 @@
       <c r="L227" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M227" s="10" t="inlineStr"/>
-      <c r="N227" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M227" s="10" t="inlineStr">
+        <is>
+          <t>mất răng hàm có cần trồng</t>
+        </is>
+      </c>
+      <c r="N227" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn về C05 để trả lời đầy đủ; ở đây chỉ định danh vấn đề và nêu các mốc hệ quả.</t>
         </is>
       </c>
       <c r="O227" s="10" t="inlineStr">
@@ -19849,7 +20940,7 @@
       </c>
       <c r="Q227" s="10" t="inlineStr">
         <is>
-          <t>Mất răng lâu năm – tiêu xương</t>
+          <t>Mất 1 răng hàm</t>
         </is>
       </c>
     </row>
@@ -19871,10 +20962,14 @@
       </c>
       <c r="D228" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E228" s="28" t="inlineStr"/>
+          <t>răng bị lung lay có giữ được không</t>
+        </is>
+      </c>
+      <c r="E228" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F228" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -19904,10 +20999,14 @@
       <c r="L228" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M228" s="10" t="inlineStr"/>
-      <c r="N228" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M228" s="10" t="inlineStr">
+        <is>
+          <t>răng lung lay giữ được không</t>
+        </is>
+      </c>
+      <c r="N228" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phụ thuộc nguyên nhân — nha chu, chấn thương hay tiêu xương. Khám sớm thì tỷ lệ giữ được cao hơn. Dẫn sang bộ Nha chu.</t>
         </is>
       </c>
       <c r="O228" s="10" t="inlineStr">
@@ -19944,10 +21043,14 @@
       </c>
       <c r="D229" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E229" s="28" t="inlineStr"/>
+          <t>vì sao mất răng lại bị tiêu xương</t>
+        </is>
+      </c>
+      <c r="E229" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F229" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -19977,10 +21080,14 @@
       <c r="L229" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M229" s="10" t="inlineStr"/>
-      <c r="N229" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M229" s="10" t="inlineStr">
+        <is>
+          <t>vì sao tiêu xương khi mất răng</t>
+        </is>
+      </c>
+      <c r="N229" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: xương ổ răng tồn tại để nâng đỡ răng; không còn lực nhai truyền xuống thì xương giảm thể tích. Khối này dùng lại cho C04 và C12.</t>
         </is>
       </c>
       <c r="O229" s="10" t="inlineStr">
@@ -20017,10 +21124,14 @@
       </c>
       <c r="D230" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E230" s="28" t="inlineStr"/>
+          <t>nhai một bên lâu ngày có hại không</t>
+        </is>
+      </c>
+      <c r="E230" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F230" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20050,10 +21161,14 @@
       <c r="L230" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M230" s="10" t="inlineStr"/>
-      <c r="N230" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M230" s="10" t="inlineStr">
+        <is>
+          <t>nhai một bên</t>
+        </is>
+      </c>
+      <c r="N230" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: gây mòn lệch, quá tải khớp thái dương hàm và tích tụ cao răng bên ít dùng. Là dấu hiệu nên đi khám.</t>
         </is>
       </c>
       <c r="O230" s="10" t="inlineStr">
@@ -20090,10 +21205,14 @@
       </c>
       <c r="D231" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E231" s="28" t="inlineStr"/>
+          <t>răng bị sâu vỡ lớn có nhổ không hay giữ lại</t>
+        </is>
+      </c>
+      <c r="E231" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F231" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20123,10 +21242,14 @@
       <c r="L231" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M231" s="10" t="inlineStr"/>
-      <c r="N231" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M231" s="10" t="inlineStr">
+        <is>
+          <t>răng sâu vỡ lớn</t>
+        </is>
+      </c>
+      <c r="N231" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: ưu tiên giữ răng thật nếu chân răng còn tốt — điều trị tuỷ và phục hình. Nhổ là lựa chọn cuối. Dẫn sang bộ Tổng quát.</t>
         </is>
       </c>
       <c r="O231" s="10" t="inlineStr">
@@ -20163,10 +21286,14 @@
       </c>
       <c r="D232" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E232" s="28" t="inlineStr"/>
+          <t>mất răng ở tuổi 30 có bình thường không</t>
+        </is>
+      </c>
+      <c r="E232" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F232" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20196,10 +21323,14 @@
       <c r="L232" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M232" s="10" t="inlineStr"/>
-      <c r="N232" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M232" s="10" t="inlineStr">
+        <is>
+          <t>mất răng tuổi 30</t>
+        </is>
+      </c>
+      <c r="N232" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: không hiếm, nguyên nhân thường là sâu răng không điều trị, nha chu hoặc chấn thương. Trấn an và hướng khám sớm.</t>
         </is>
       </c>
       <c r="O232" s="10" t="inlineStr">
@@ -20236,10 +21367,14 @@
       </c>
       <c r="D233" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E233" s="28" t="inlineStr"/>
+          <t>răng khôn mọc lệch có cần nhổ không</t>
+        </is>
+      </c>
+      <c r="E233" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F233" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20269,10 +21404,14 @@
       <c r="L233" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M233" s="10" t="inlineStr"/>
-      <c r="N233" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M233" s="10" t="inlineStr">
+        <is>
+          <t>răng khôn mọc lệch</t>
+        </is>
+      </c>
+      <c r="N233" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn sang bộ Nha khoa tổng quát; ở bộ implant chỉ nêu liên hệ: nhổ răng khôn lệch giúp bảo vệ răng số 7 kế bên khỏi sâu và tiêu xương.</t>
         </is>
       </c>
       <c r="O233" s="10" t="inlineStr">
@@ -20309,10 +21448,14 @@
       </c>
       <c r="D234" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E234" s="28" t="inlineStr"/>
+          <t>hôi miệng kéo dài là dấu hiệu bệnh gì</t>
+        </is>
+      </c>
+      <c r="E234" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F234" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20342,10 +21485,14 @@
       <c r="L234" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M234" s="10" t="inlineStr"/>
-      <c r="N234" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M234" s="10" t="inlineStr">
+        <is>
+          <t>hôi miệng kéo dài</t>
+        </is>
+      </c>
+      <c r="N234" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: thường liên quan mảng bám, nha chu hoặc ổ nhiễm trùng quanh răng. Dẫn sang bộ Nha chu.</t>
         </is>
       </c>
       <c r="O234" s="10" t="inlineStr">
@@ -20382,10 +21529,14 @@
       </c>
       <c r="D235" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E235" s="28" t="inlineStr"/>
+          <t>mặt bị lệch có liên quan đến mất răng không</t>
+        </is>
+      </c>
+      <c r="E235" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F235" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20415,10 +21566,14 @@
       <c r="L235" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M235" s="10" t="inlineStr"/>
-      <c r="N235" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M235" s="10" t="inlineStr">
+        <is>
+          <t>mặt lệch do mất răng</t>
+        </is>
+      </c>
+      <c r="N235" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nhai lệch lâu ngày do mất răng một bên có thể làm cơ nhai phát triển không đều. Trình bày thận trọng, cần BS thẩm định.</t>
         </is>
       </c>
       <c r="O235" s="10" t="inlineStr">
@@ -20428,7 +21583,7 @@
       </c>
       <c r="P235" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R4 · Cần BS thẩm định</t>
         </is>
       </c>
       <c r="Q235" s="10" t="inlineStr">
@@ -20455,10 +21610,14 @@
       </c>
       <c r="D236" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E236" s="28" t="inlineStr"/>
+          <t>ê buốt răng kéo dài có nguy hiểm không</t>
+        </is>
+      </c>
+      <c r="E236" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F236" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20488,10 +21647,14 @@
       <c r="L236" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M236" s="10" t="inlineStr"/>
-      <c r="N236" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M236" s="10" t="inlineStr">
+        <is>
+          <t>ê buốt răng kéo dài</t>
+        </is>
+      </c>
+      <c r="N236" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là dấu hiệu nên khám — có thể do mòn cổ răng, tụt lợi hoặc tuỷ đang viêm. Dẫn sang bộ Tổng quát.</t>
         </is>
       </c>
       <c r="O236" s="10" t="inlineStr">
@@ -20528,10 +21691,14 @@
       </c>
       <c r="D237" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E237" s="28" t="inlineStr"/>
+          <t>tự kiểm tra sức khoẻ răng miệng tại nhà thế nào</t>
+        </is>
+      </c>
+      <c r="E237" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F237" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20561,10 +21728,14 @@
       <c r="L237" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M237" s="10" t="inlineStr"/>
-      <c r="N237" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M237" s="10" t="inlineStr">
+        <is>
+          <t>tự kiểm tra răng miệng</t>
+        </is>
+      </c>
+      <c r="N237" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: checklist 6 dấu hiệu tự quan sát được — chảy máu khi chải, lợi sưng đỏ, răng lung lay, hôi miệng dai dẳng, ê buốt, răng đổi màu. Liên kết tới công cụ kiểm tra online làm micro-conversion.</t>
         </is>
       </c>
       <c r="O237" s="10" t="inlineStr">
@@ -20601,10 +21772,14 @@
       </c>
       <c r="D238" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E238" s="28" t="inlineStr"/>
+          <t>bao lâu nên đi khám răng một lần</t>
+        </is>
+      </c>
+      <c r="E238" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F238" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20634,10 +21809,14 @@
       <c r="L238" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M238" s="10" t="inlineStr"/>
-      <c r="N238" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M238" s="10" t="inlineStr">
+        <is>
+          <t>khám răng bao lâu một lần</t>
+        </is>
+      </c>
+      <c r="N238" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: 6 tháng một lần với người bình thường. Nội dung nền, CTA mềm.</t>
         </is>
       </c>
       <c r="O238" s="10" t="inlineStr">
@@ -20674,10 +21853,14 @@
       </c>
       <c r="D239" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E239" s="28" t="inlineStr"/>
+          <t>răng giả tháo lắp và răng cố định khác nhau thế nào</t>
+        </is>
+      </c>
+      <c r="E239" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F239" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20707,10 +21890,14 @@
       <c r="L239" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M239" s="10" t="inlineStr"/>
-      <c r="N239" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M239" s="10" t="inlineStr">
+        <is>
+          <t>răng tháo lắp và cố định</t>
+        </is>
+      </c>
+      <c r="N239" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: khác ở cách giữ (tháo ra được hay không), cảm giác nhai và ảnh hưởng tới xương. Bài nền, dẫn sang C05 để so sánh đầy đủ.</t>
         </is>
       </c>
       <c r="O239" s="10" t="inlineStr">
@@ -20747,10 +21934,14 @@
       </c>
       <c r="D240" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E240" s="28" t="inlineStr"/>
+          <t>mất răng có di truyền không</t>
+        </is>
+      </c>
+      <c r="E240" s="28" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
       <c r="F240" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20780,10 +21971,14 @@
       <c r="L240" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M240" s="10" t="inlineStr"/>
-      <c r="N240" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M240" s="10" t="inlineStr">
+        <is>
+          <t>mất răng di truyền</t>
+        </is>
+      </c>
+      <c r="N240" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: yếu tố di truyền ảnh hưởng tới nguy cơ nha chu và chất lượng men răng, nhưng vệ sinh và thói quen quyết định nhiều hơn.</t>
         </is>
       </c>
       <c r="O240" s="10" t="inlineStr">
@@ -20820,10 +22015,14 @@
       </c>
       <c r="D241" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E241" s="28" t="inlineStr"/>
+          <t>trẻ mất răng sữa sớm có ảnh hưởng gì</t>
+        </is>
+      </c>
+      <c r="E241" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F241" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20853,10 +22052,14 @@
       <c r="L241" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M241" s="10" t="inlineStr"/>
-      <c r="N241" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M241" s="10" t="inlineStr">
+        <is>
+          <t>mất răng sữa sớm</t>
+        </is>
+      </c>
+      <c r="N241" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dẫn sang bộ Nha khoa trẻ em — mất răng sữa sớm làm răng vĩnh viễn mọc lệch. Chỉ nêu một câu liên hệ.</t>
         </is>
       </c>
       <c r="O241" s="10" t="inlineStr">
@@ -20893,10 +22096,14 @@
       </c>
       <c r="D242" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E242" s="28" t="inlineStr"/>
+          <t>ăn uống thế nào để giữ răng lâu dài</t>
+        </is>
+      </c>
+      <c r="E242" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F242" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20926,10 +22133,14 @@
       <c r="L242" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M242" s="10" t="inlineStr"/>
-      <c r="N242" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M242" s="10" t="inlineStr">
+        <is>
+          <t>ăn uống giữ răng</t>
+        </is>
+      </c>
+      <c r="N242" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: hạn chế đường và đồ uống có ga, uống đủ nước, không dùng răng mở nắp. Nội dung nền tái sử dụng cho nhiều bộ.</t>
         </is>
       </c>
       <c r="O242" s="10" t="inlineStr">
@@ -20966,10 +22177,14 @@
       </c>
       <c r="D243" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E243" s="28" t="inlineStr"/>
+          <t>trồng răng implant có đau lắm không nghe nói khoan vào xương rất ghê</t>
+        </is>
+      </c>
+      <c r="E243" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F243" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -20999,10 +22214,14 @@
       <c r="L243" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M243" s="10" t="inlineStr"/>
-      <c r="N243" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M243" s="10" t="inlineStr">
+        <is>
+          <t>quan niệm implant đau</t>
+        </is>
+      </c>
+      <c r="N243" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm — cảm giác trong lúc làm được kiểm soát bằng gây tê; điều khách thật sự nên quan tâm là giai đoạn sau khi hết tê và cách giảm sưng đau. Không dùng chữ “không đau”.</t>
         </is>
       </c>
       <c r="O243" s="10" t="inlineStr">
@@ -21012,7 +22231,7 @@
       </c>
       <c r="P243" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R1 · Cấm “không đau”</t>
         </is>
       </c>
       <c r="Q243" s="10" t="inlineStr">
@@ -21039,10 +22258,14 @@
       </c>
       <c r="D244" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E244" s="28" t="inlineStr"/>
+          <t>có phải trồng răng implant là của nhà giàu không</t>
+        </is>
+      </c>
+      <c r="E244" s="28" t="inlineStr">
+        <is>
+          <t>Chi phí</t>
+        </is>
+      </c>
       <c r="F244" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21072,10 +22295,14 @@
       <c r="L244" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M244" s="10" t="inlineStr"/>
-      <c r="N244" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M244" s="10" t="inlineStr">
+        <is>
+          <t>implant cho người thu nhập trung bình</t>
+        </is>
+      </c>
+      <c r="N244" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm bằng cách nêu các phương án theo ngân sách và chương trình trả góp; không nêu con số. Tránh giọng bán hàng.</t>
         </is>
       </c>
       <c r="O244" s="10" t="inlineStr">
@@ -21085,7 +22312,7 @@
       </c>
       <c r="P244" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R12 · Không ghi số; R0 giọng giáo dục</t>
         </is>
       </c>
       <c r="Q244" s="10" t="inlineStr">
@@ -21112,10 +22339,14 @@
       </c>
       <c r="D245" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E245" s="28" t="inlineStr"/>
+          <t>đắp thuốc nam chữa răng lung lay có khỏi không</t>
+        </is>
+      </c>
+      <c r="E245" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F245" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21145,10 +22376,14 @@
       <c r="L245" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M245" s="10" t="inlineStr"/>
-      <c r="N245" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M245" s="10" t="inlineStr">
+        <is>
+          <t>thuốc nam chữa răng lung lay</t>
+        </is>
+      </c>
+      <c r="N245" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: viết để CẢNH BÁO — đắp thuốc lên lợi không xử lý được nguyên nhân (nha chu, tiêu xương) và có thể gây bỏng niêm mạc, chậm trễ điều trị. Giọng tôn trọng, không chế giễu.</t>
         </is>
       </c>
       <c r="O245" s="10" t="inlineStr">
@@ -21185,10 +22420,14 @@
       </c>
       <c r="D246" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E246" s="28" t="inlineStr"/>
+          <t>ngậm nước muối có chữa được viêm lợi quanh răng giả không</t>
+        </is>
+      </c>
+      <c r="E246" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F246" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21218,10 +22457,14 @@
       <c r="L246" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M246" s="10" t="inlineStr"/>
-      <c r="N246" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M246" s="10" t="inlineStr">
+        <is>
+          <t>nước muối chữa viêm lợi</t>
+        </is>
+      </c>
+      <c r="N246" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: nước muối hỗ trợ làm dịu tạm thời, KHÔNG thay được việc làm sạch cơ học và điều trị. Nêu rõ giới hạn thay vì phủ nhận hoàn toàn.</t>
         </is>
       </c>
       <c r="O246" s="10" t="inlineStr">
@@ -21258,10 +22501,14 @@
       </c>
       <c r="D247" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E247" s="28" t="inlineStr"/>
+          <t>có nên nhổ hết răng rồi làm răng giả cho khoẻ không</t>
+        </is>
+      </c>
+      <c r="E247" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F247" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21291,10 +22538,14 @@
       <c r="L247" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M247" s="10" t="inlineStr"/>
-      <c r="N247" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M247" s="10" t="inlineStr">
+        <is>
+          <t>nhổ hết răng làm răng giả</t>
+        </is>
+      </c>
+      <c r="N247" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm phổ biến ở người lớn tuổi — nhổ hết làm xương tiêu nhanh và hàm giả ngày càng lỏng. Giữ được răng thật nào thì giữ.</t>
         </is>
       </c>
       <c r="O247" s="10" t="inlineStr">
@@ -21309,7 +22560,7 @@
       </c>
       <c r="Q247" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
     </row>
@@ -21331,10 +22582,14 @@
       </c>
       <c r="D248" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E248" s="28" t="inlineStr"/>
+          <t>người già thì không cần trồng răng nữa đúng không</t>
+        </is>
+      </c>
+      <c r="E248" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F248" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21364,10 +22619,14 @@
       <c r="L248" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M248" s="10" t="inlineStr"/>
-      <c r="N248" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M248" s="10" t="inlineStr">
+        <is>
+          <t>người già có cần trồng răng</t>
+        </is>
+      </c>
+      <c r="N248" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm — ăn nhai ảnh hưởng dinh dưỡng và chất lượng sống ở mọi tuổi. Phương án tuỳ sức khoẻ, không tuỳ tuổi.</t>
         </is>
       </c>
       <c r="O248" s="10" t="inlineStr">
@@ -21382,7 +22641,7 @@
       </c>
       <c r="Q248" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Bệnh lý nền &amp; người cao tuổi</t>
         </is>
       </c>
     </row>
@@ -21404,10 +22663,14 @@
       </c>
       <c r="D249" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E249" s="28" t="inlineStr"/>
+          <t>trồng răng implant xong là xong luôn không cần quan tâm nữa phải không</t>
+        </is>
+      </c>
+      <c r="E249" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F249" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21437,10 +22700,14 @@
       <c r="L249" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M249" s="10" t="inlineStr"/>
-      <c r="N249" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M249" s="10" t="inlineStr">
+        <is>
+          <t>quan niệm implant không cần chăm</t>
+        </is>
+      </c>
+      <c r="N249" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm nguy hiểm nhất — implant cần vệ sinh và tái khám như răng thật, thậm chí kỹ hơn ở vùng cổ trụ.</t>
         </is>
       </c>
       <c r="O249" s="10" t="inlineStr">
@@ -21477,10 +22744,14 @@
       </c>
       <c r="D250" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E250" s="28" t="inlineStr"/>
+          <t>răng giả có ăn được đồ cứng như răng thật không</t>
+        </is>
+      </c>
+      <c r="E250" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F250" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21510,10 +22781,14 @@
       <c r="L250" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M250" s="10" t="inlineStr"/>
-      <c r="N250" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M250" s="10" t="inlineStr">
+        <is>
+          <t>răng giả ăn đồ cứng</t>
+        </is>
+      </c>
+      <c r="N250" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phân biệt rõ ba loại phục hình — implant chịu lực tốt nhất, cầu răng trung bình, tháo lắp kém nhất. Không loại nào nên cắn vật quá cứng.</t>
         </is>
       </c>
       <c r="O250" s="10" t="inlineStr">
@@ -21550,10 +22825,14 @@
       </c>
       <c r="D251" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E251" s="28" t="inlineStr"/>
+          <t>cắm răng giả vào xương có bị ảnh hưởng não không</t>
+        </is>
+      </c>
+      <c r="E251" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F251" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21583,10 +22862,14 @@
       <c r="L251" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M251" s="10" t="inlineStr"/>
-      <c r="N251" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M251" s="10" t="inlineStr">
+        <is>
+          <t>implant ảnh hưởng não</t>
+        </is>
+      </c>
+      <c r="N251" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa hiểu nhầm — trụ nằm trong xương ổ răng, cách xa cấu trúc nội sọ. Giải thích bằng giải phẫu đơn giản thay vì bác bỏ suông.</t>
         </is>
       </c>
       <c r="O251" s="10" t="inlineStr">
@@ -21623,10 +22906,14 @@
       </c>
       <c r="D252" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E252" s="28" t="inlineStr"/>
+          <t>có phải trồng răng xong là không bao giờ hỏng nữa không</t>
+        </is>
+      </c>
+      <c r="E252" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F252" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21656,10 +22943,14 @@
       <c r="L252" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M252" s="10" t="inlineStr"/>
-      <c r="N252" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M252" s="10" t="inlineStr">
+        <is>
+          <t>implant có hỏng không</t>
+        </is>
+      </c>
+      <c r="N252" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm — implant có thể hỏng; tỷ lệ thấp nhưng không phải bằng không. Dẫn sang C06 và C11.</t>
         </is>
       </c>
       <c r="O252" s="10" t="inlineStr">
@@ -21669,7 +22960,7 @@
       </c>
       <c r="P252" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R1 · Không cam kết</t>
         </is>
       </c>
       <c r="Q252" s="10" t="inlineStr">
@@ -21696,10 +22987,14 @@
       </c>
       <c r="D253" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E253" s="28" t="inlineStr"/>
+          <t>mẹo làm chắc răng tại nhà có hiệu quả không</t>
+        </is>
+      </c>
+      <c r="E253" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F253" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21729,10 +23024,14 @@
       <c r="L253" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M253" s="10" t="inlineStr"/>
-      <c r="N253" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M253" s="10" t="inlineStr">
+        <is>
+          <t>mẹo làm chắc răng</t>
+        </is>
+      </c>
+      <c r="N253" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: phân loại mẹo nào vô hại, mẹo nào có hại (chà chanh, muối hột, baking soda thô). Giọng tôn trọng.</t>
         </is>
       </c>
       <c r="O253" s="10" t="inlineStr">
@@ -21769,10 +23068,14 @@
       </c>
       <c r="D254" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E254" s="28" t="inlineStr"/>
+          <t>trồng răng có phải kiêng cữ như sau phẫu thuật lớn không</t>
+        </is>
+      </c>
+      <c r="E254" s="28" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
       <c r="F254" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21802,10 +23105,14 @@
       <c r="L254" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M254" s="10" t="inlineStr"/>
-      <c r="N254" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M254" s="10" t="inlineStr">
+        <is>
+          <t>kiêng cữ sau trồng răng</t>
+        </is>
+      </c>
+      <c r="N254" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: là tiểu phẫu, kiêng cữ ở mức hợp lý chứ không cần kiêng khem cực đoan. Sửa quan niệm kiêng tắm, kiêng gió.</t>
         </is>
       </c>
       <c r="O254" s="10" t="inlineStr">
@@ -21842,10 +23149,14 @@
       </c>
       <c r="D255" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E255" s="28" t="inlineStr"/>
+          <t>nhổ răng có bị hại mắt không</t>
+        </is>
+      </c>
+      <c r="E255" s="28" t="inlineStr">
+        <is>
+          <t>Rủi ro</t>
+        </is>
+      </c>
       <c r="F255" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21875,10 +23186,14 @@
       <c r="L255" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M255" s="10" t="inlineStr"/>
-      <c r="N255" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M255" s="10" t="inlineStr">
+        <is>
+          <t>nhổ răng hại mắt</t>
+        </is>
+      </c>
+      <c r="N255" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: sửa quan niệm dân gian — không có cơ sở giải phẫu cho việc nhổ răng gây hại thị lực. Giải thích ngắn gọn, không chế giễu.</t>
         </is>
       </c>
       <c r="O255" s="10" t="inlineStr">
@@ -21915,10 +23230,14 @@
       </c>
       <c r="D256" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E256" s="28" t="inlineStr"/>
+          <t>răng implant có bị đen viền như răng sứ không</t>
+        </is>
+      </c>
+      <c r="E256" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F256" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -21948,10 +23267,14 @@
       <c r="L256" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M256" s="10" t="inlineStr"/>
-      <c r="N256" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M256" s="10" t="inlineStr">
+        <is>
+          <t>implant có đen viền không</t>
+        </is>
+      </c>
+      <c r="N256" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: đen viền ở răng sứ thường do sườn kim loại; mão trên implant dùng toàn sứ thì không có vấn đề này, nhưng tụt lợi vẫn có thể lộ phần kim loại của abutment. Dẫn sang bộ Răng sứ.</t>
         </is>
       </c>
       <c r="O256" s="10" t="inlineStr">
@@ -21988,10 +23311,14 @@
       </c>
       <c r="D257" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E257" s="28" t="inlineStr"/>
+          <t>có nên tin quảng cáo trồng răng giá rẻ trên mạng không</t>
+        </is>
+      </c>
+      <c r="E257" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm chứng</t>
+        </is>
+      </c>
       <c r="F257" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -22021,10 +23348,14 @@
       <c r="L257" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M257" s="10" t="inlineStr"/>
-      <c r="N257" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M257" s="10" t="inlineStr">
+        <is>
+          <t>quảng cáo trồng răng giá rẻ</t>
+        </is>
+      </c>
+      <c r="N257" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: dạy cách kiểm chứng thay vì cảnh báo chung chung — hỏi hãng trụ, yêu cầu báo giá tách 3 khoản, kiểm tra giấy phép cơ sở. Không nêu tên nơi nào.</t>
         </is>
       </c>
       <c r="O257" s="10" t="inlineStr">
@@ -22034,7 +23365,7 @@
       </c>
       <c r="P257" s="10" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>R6 · Không nêu tên</t>
         </is>
       </c>
       <c r="Q257" s="10" t="inlineStr">
@@ -22061,10 +23392,14 @@
       </c>
       <c r="D258" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E258" s="28" t="inlineStr"/>
+          <t>làm răng ở nước ngoài có tốt hơn trong nước không</t>
+        </is>
+      </c>
+      <c r="E258" s="28" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
       <c r="F258" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -22094,10 +23429,14 @@
       <c r="L258" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M258" s="10" t="inlineStr"/>
-      <c r="N258" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M258" s="10" t="inlineStr">
+        <is>
+          <t>làm răng ở nước ngoài</t>
+        </is>
+      </c>
+      <c r="N258" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: điều quan trọng với implant là khả năng TÁI KHÁM và xử lý sự cố dài hạn — làm xa gây khó khăn ở điểm này. Trình bày khách quan, không hạ thấp.</t>
         </is>
       </c>
       <c r="O258" s="10" t="inlineStr">
@@ -22112,7 +23451,7 @@
       </c>
       <c r="Q258" s="10" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Khách tỉnh &amp; Việt kiều</t>
         </is>
       </c>
     </row>
@@ -22134,10 +23473,14 @@
       </c>
       <c r="D259" s="29" t="inlineStr">
         <is>
-          <t>[CẦN VIẾT]</t>
-        </is>
-      </c>
-      <c r="E259" s="28" t="inlineStr"/>
+          <t>trồng răng vào ngày tốt có ảnh hưởng kết quả không</t>
+        </is>
+      </c>
+      <c r="E259" s="28" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
       <c r="F259" s="28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -22167,10 +23510,14 @@
       <c r="L259" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M259" s="10" t="inlineStr"/>
-      <c r="N259" s="31" t="inlineStr">
-        <is>
-          <t>[CẦN VIẾT brief: BLUF + số liệu + điều bất lợi]</t>
+      <c r="M259" s="10" t="inlineStr">
+        <is>
+          <t>ngày tốt trồng răng</t>
+        </is>
+      </c>
+      <c r="N259" s="10" t="inlineStr">
+        <is>
+          <t>BLUF: tôn trọng niềm tin cá nhân nhưng nêu rõ yếu tố quyết định kết quả là chỉ định đúng, kỹ thuật và chăm sóc sau đó.</t>
         </is>
       </c>
       <c r="O259" s="10" t="inlineStr">
@@ -22421,12 +23768,12 @@
           <t>BS Implant + Pháp chế</t>
         </is>
       </c>
-      <c r="O5" s="32" t="inlineStr">
+      <c r="O5" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P5" s="33" t="inlineStr"/>
+      <c r="P5" s="32" t="inlineStr"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="23" t="n">
@@ -22489,12 +23836,12 @@
           <t>BS Implant + Pháp chế</t>
         </is>
       </c>
-      <c r="O6" s="32" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P6" s="33" t="inlineStr"/>
+      <c r="P6" s="32" t="inlineStr"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="23" t="n">
@@ -22557,12 +23904,12 @@
           <t>BS Implant + Kho vật tư + Pháp chế</t>
         </is>
       </c>
-      <c r="O7" s="32" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P7" s="33" t="inlineStr"/>
+      <c r="P7" s="32" t="inlineStr"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="23" t="n">
@@ -22625,12 +23972,12 @@
           <t>Sale ops + Pháp chế</t>
         </is>
       </c>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="O8" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P8" s="33" t="inlineStr"/>
+      <c r="P8" s="32" t="inlineStr"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="23" t="n">
@@ -22693,12 +24040,12 @@
           <t>Pháp chế + SEO</t>
         </is>
       </c>
-      <c r="O9" s="32" t="inlineStr">
+      <c r="O9" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P9" s="33" t="inlineStr"/>
+      <c r="P9" s="32" t="inlineStr"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="24" t="n">
@@ -22763,12 +24110,12 @@
           <t>SEO + Pháp chế</t>
         </is>
       </c>
-      <c r="O10" s="32" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P10" s="33" t="inlineStr"/>
+      <c r="P10" s="32" t="inlineStr"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="25" t="n">
@@ -22833,12 +24180,12 @@
           <t>BS Implant + Content lead</t>
         </is>
       </c>
-      <c r="O11" s="32" t="inlineStr">
+      <c r="O11" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P11" s="33" t="inlineStr"/>
+      <c r="P11" s="32" t="inlineStr"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="24" t="n">
@@ -22903,12 +24250,12 @@
           <t>BS Implant</t>
         </is>
       </c>
-      <c r="O12" s="32" t="inlineStr">
+      <c r="O12" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P12" s="33" t="inlineStr"/>
+      <c r="P12" s="32" t="inlineStr"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="25" t="n">
@@ -22973,12 +24320,12 @@
           <t>Team Content</t>
         </is>
       </c>
-      <c r="O13" s="32" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P13" s="33" t="inlineStr"/>
+      <c r="P13" s="32" t="inlineStr"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="24" t="n">
@@ -23043,12 +24390,12 @@
           <t>BS Implant + Pháp chế</t>
         </is>
       </c>
-      <c r="O14" s="32" t="inlineStr">
+      <c r="O14" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P14" s="33" t="inlineStr"/>
+      <c r="P14" s="32" t="inlineStr"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="25" t="n">
@@ -23115,12 +24462,12 @@
           <t>CSKH</t>
         </is>
       </c>
-      <c r="O15" s="32" t="inlineStr">
+      <c r="O15" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P15" s="33" t="inlineStr"/>
+      <c r="P15" s="32" t="inlineStr"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="24" t="n">
@@ -23187,12 +24534,12 @@
           <t>BS Implant</t>
         </is>
       </c>
-      <c r="O16" s="32" t="inlineStr">
+      <c r="O16" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P16" s="33" t="inlineStr"/>
+      <c r="P16" s="32" t="inlineStr"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="25" t="n">
@@ -23259,12 +24606,12 @@
           <t>CSKH</t>
         </is>
       </c>
-      <c r="O17" s="32" t="inlineStr">
+      <c r="O17" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P17" s="33" t="inlineStr"/>
+      <c r="P17" s="32" t="inlineStr"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="24" t="n">
@@ -23331,12 +24678,12 @@
           <t>Team Content</t>
         </is>
       </c>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="O18" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P18" s="33" t="inlineStr"/>
+      <c r="P18" s="32" t="inlineStr"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="25" t="n">
@@ -23403,12 +24750,12 @@
           <t>Team Content</t>
         </is>
       </c>
-      <c r="O19" s="32" t="inlineStr">
+      <c r="O19" s="31" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="P19" s="33" t="inlineStr"/>
+      <c r="P19" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -23475,7 +24822,7 @@
           <t>Tháng đo:</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>⚠ Chưa đo — tháng Setup là tháng lấy mốc gốc</t>
         </is>
@@ -23557,17 +24904,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
       <c r="I6" s="13" t="n"/>
-      <c r="J6" s="33" t="n"/>
+      <c r="J6" s="32" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>implant bị gãy trụ có lấy ra được không</t>
         </is>
@@ -23587,11 +24934,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
       <c r="I7" s="9" t="n"/>
-      <c r="J7" s="33" t="n"/>
+      <c r="J7" s="32" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="13" t="n">
@@ -23617,17 +24964,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
       <c r="I8" s="13" t="n"/>
-      <c r="J8" s="33" t="n"/>
+      <c r="J8" s="32" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>sau khi tháo trụ bao lâu thì cấy lại được</t>
         </is>
@@ -23647,11 +24994,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
       <c r="I9" s="9" t="n"/>
-      <c r="J9" s="33" t="n"/>
+      <c r="J9" s="32" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="13" t="n">
@@ -23677,17 +25024,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
       <c r="I10" s="13" t="n"/>
-      <c r="J10" s="33" t="n"/>
+      <c r="J10" s="32" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>implant có gây hôi miệng không</t>
         </is>
@@ -23707,11 +25054,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
       <c r="I11" s="9" t="n"/>
-      <c r="J11" s="33" t="n"/>
+      <c r="J11" s="32" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="13" t="n">
@@ -23737,17 +25084,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
       <c r="I12" s="13" t="n"/>
-      <c r="J12" s="33" t="n"/>
+      <c r="J12" s="32" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>cấy implant có phải nằm viện không</t>
         </is>
@@ -23767,11 +25114,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="34" t="n"/>
       <c r="I13" s="9" t="n"/>
-      <c r="J13" s="33" t="n"/>
+      <c r="J13" s="32" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -23797,17 +25144,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="34" t="n"/>
       <c r="I14" s="13" t="n"/>
-      <c r="J14" s="33" t="n"/>
+      <c r="J14" s="32" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>xương nhân tạo có an toàn không</t>
         </is>
@@ -23827,11 +25174,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="33" t="n"/>
+      <c r="J15" s="32" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="13" t="n">
@@ -23857,17 +25204,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
       <c r="I16" s="13" t="n"/>
-      <c r="J16" s="33" t="n"/>
+      <c r="J16" s="32" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>mão sứ trên implant nên chọn loại nào</t>
         </is>
@@ -23887,11 +25234,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="34" t="n"/>
+      <c r="H17" s="34" t="n"/>
       <c r="I17" s="9" t="n"/>
-      <c r="J17" s="33" t="n"/>
+      <c r="J17" s="32" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="13" t="n">
@@ -23917,17 +25264,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+      <c r="H18" s="34" t="n"/>
       <c r="I18" s="13" t="n"/>
-      <c r="J18" s="33" t="n"/>
+      <c r="J18" s="32" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>bảng giá trồng răng implant 2027</t>
         </is>
@@ -23947,11 +25294,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="34" t="n"/>
+      <c r="H19" s="34" t="n"/>
       <c r="I19" s="9" t="n"/>
-      <c r="J19" s="33" t="n"/>
+      <c r="J19" s="32" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -23977,17 +25324,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
       <c r="I20" s="13" t="n"/>
-      <c r="J20" s="33" t="n"/>
+      <c r="J20" s="32" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>giá implant đã bao gồm mão sứ chưa</t>
         </is>
@@ -24007,11 +25354,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="34" t="n"/>
+      <c r="H21" s="34" t="n"/>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="33" t="n"/>
+      <c r="J21" s="32" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="13" t="n">
@@ -24037,17 +25384,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="34" t="n"/>
       <c r="I22" s="13" t="n"/>
-      <c r="J22" s="33" t="n"/>
+      <c r="J22" s="32" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>bác sĩ implant giỏi ở Hà Nội</t>
         </is>
@@ -24067,11 +25414,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="34" t="n"/>
+      <c r="H23" s="34" t="n"/>
       <c r="I23" s="9" t="n"/>
-      <c r="J23" s="33" t="n"/>
+      <c r="J23" s="32" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="13" t="n">
@@ -24097,17 +25444,17 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
+      <c r="F24" s="34" t="n"/>
+      <c r="G24" s="34" t="n"/>
+      <c r="H24" s="34" t="n"/>
       <c r="I24" s="13" t="n"/>
-      <c r="J24" s="33" t="n"/>
+      <c r="J24" s="32" t="n"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>nha khoa Paris có giấy phép gì</t>
         </is>
@@ -24127,11 +25474,11 @@
           <t>A · CORE 80/20</t>
         </is>
       </c>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="34" t="n"/>
+      <c r="H25" s="34" t="n"/>
       <c r="I25" s="9" t="n"/>
-      <c r="J25" s="33" t="n"/>
+      <c r="J25" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -24264,7 +25611,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0</v>
@@ -24274,7 +25621,7 @@
           <t>Content lead</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24286,7 +25633,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Cam kết kết quả &amp; mức độ đau</t>
         </is>
@@ -24303,7 +25650,7 @@
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>C03 C06 C09 C11 C14</t>
+          <t>C02 C03 C06 C09 C10 C11 C14</t>
         </is>
       </c>
       <c r="F6" s="15" t="n">
@@ -24317,7 +25664,7 @@
           <t>Pháp chế</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24350,7 +25697,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>7</v>
@@ -24360,7 +25707,7 @@
           <t>Pháp chế + Chuyên môn</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24389,11 +25736,11 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>C03 C07 C08 C11 C14</t>
+          <t>C03 C07 C08 C11 C14 C15</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>6</v>
@@ -24403,7 +25750,7 @@
           <t>Pháp chế</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24432,11 +25779,11 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>C08 C12 C14</t>
+          <t>C01 C08 C12 C14</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>5</v>
@@ -24446,7 +25793,7 @@
           <t>Chuyên môn + HR</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24489,7 +25836,7 @@
           <t>CSKH + Pháp chế</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24518,11 +25865,11 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>C03 C05 C07 C08 C11 C14</t>
+          <t>C02 C03 C04 C05 C07 C08 C11 C14</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>10</v>
@@ -24532,7 +25879,7 @@
           <t>Pháp chế</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24544,7 +25891,7 @@
           <t>R7</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>“CHÍNH HÃNG” &amp; vật tư ⚠ đặc thù nha khoa</t>
         </is>
@@ -24561,11 +25908,11 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>C03 C14</t>
+          <t>C03 C04 C14</t>
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>14</v>
@@ -24575,7 +25922,7 @@
           <t>Kho vật tư + Pháp chế</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24608,7 +25955,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -24618,7 +25965,7 @@
           <t>Pháp chế</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24630,7 +25977,7 @@
           <t>R9</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Giấy xác nhận nội dung quảng cáo</t>
         </is>
@@ -24661,7 +26008,7 @@
           <t>Pháp chế (Sở Y tế)</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24704,7 +26051,7 @@
           <t>Brand + Pháp chế</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24747,7 +26094,7 @@
           <t>Brand + Pháp chế</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24759,7 +26106,7 @@
           <t>R12</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>GIÁ · ƯU ĐÃI · TRẢ GÓP = dữ liệu động ⚠ đặc thù Paris</t>
         </is>
@@ -24776,11 +26123,11 @@
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>C03 C07 C11 C14 C15</t>
+          <t>C02 C03 C04 C07 C11 C14 C15</t>
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>15</v>
@@ -24790,7 +26137,7 @@
           <t>Sale ops + Pháp chế</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24819,11 +26166,11 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>C04 C06 C07 C09 C10 C11 C13</t>
+          <t>C04 C05 C06 C07 C09 C10 C11 C13</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>7</v>
@@ -24833,7 +26180,7 @@
           <t>Chuyên môn + Pháp chế</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -24855,7 +26202,7 @@
       <c r="I20" s="5" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Content/Chi nhánh soạn → tự kiểm checklist R0–R13 → BS thẩm định chuyên môn → Pháp chế duyệt nội dung, hình ảnh và chữ “chính hãng” → (nếu là quảng cáo dịch vụ KCB) xin GXNNDQC tại Sở Y tế → phát hành → lưu hồ sơ.  ⚠ Mọi đầu việc phải CỘNG thời gian duyệt 2 lớp vào hạn chót.</t>
         </is>
